--- a/trades/live_and_forward_trades.xlsx
+++ b/trades/live_and_forward_trades.xlsx
@@ -687,7 +687,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Generated on 2026-10-29 00:45:39 IST | All Active Strategies Analyzed</t>
+          <t>Generated on 2026-10-29 01:58:46 IST | All Active Strategies Analyzed</t>
         </is>
       </c>
     </row>
@@ -773,10 +773,10 @@
         <v>377.6</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>19610</v>
+        <v>25560</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>4.74</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
@@ -809,10 +809,10 @@
         <v>147.1</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>8948</v>
+        <v>11922</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>7.35</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
@@ -845,10 +845,10 @@
         <v>230.5</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>10662</v>
+        <v>13638</v>
       </c>
       <c r="K8" s="17" t="n">
-        <v>3.78</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
@@ -949,7 +949,7 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="D2" s="25" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E2" s="24" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="D3" s="32" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E3" s="31" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="P3" s="32" t="inlineStr">
         <is>
-          <t>NIFTY 22750 PE</t>
+          <t>NIFTY 22650 PE</t>
         </is>
       </c>
       <c r="Q3" s="31" t="inlineStr">
@@ -1281,28 +1281,28 @@
         </is>
       </c>
       <c r="R3" s="33" t="n">
-        <v>224.12</v>
+        <v>176.29</v>
       </c>
       <c r="S3" s="33" t="n">
-        <v>253.31</v>
+        <v>201.28</v>
       </c>
       <c r="T3" s="35" t="n">
-        <v>14568</v>
+        <v>45835</v>
       </c>
       <c r="U3" s="35" t="n">
-        <v>16465</v>
+        <v>52333</v>
       </c>
       <c r="V3" s="36" t="n">
-        <v>1820</v>
+        <v>6356</v>
       </c>
       <c r="W3" s="37" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="X3" s="31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y3" s="31" t="n">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="Z3" s="32" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="P4" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 22800 CE</t>
+          <t>NIFTY 22900 CE</t>
         </is>
       </c>
       <c r="Q4" s="24" t="inlineStr">
@@ -1383,28 +1383,28 @@
         </is>
       </c>
       <c r="R4" s="26" t="n">
-        <v>208.75</v>
+        <v>164.2</v>
       </c>
       <c r="S4" s="26" t="n">
-        <v>208.59</v>
+        <v>164.05</v>
       </c>
       <c r="T4" s="28" t="n">
-        <v>27138</v>
+        <v>42692</v>
       </c>
       <c r="U4" s="28" t="n">
-        <v>27117</v>
+        <v>42653</v>
       </c>
       <c r="V4" s="39" t="n">
-        <v>-118</v>
+        <v>-166</v>
       </c>
       <c r="W4" s="40" t="n">
         <v>-0.4</v>
       </c>
       <c r="X4" s="24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y4" s="24" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z4" s="25" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D5" s="32" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E5" s="31" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="P5" s="32" t="inlineStr">
         <is>
-          <t>NIFTY 22550 PE</t>
+          <t>NIFTY 22450 PE</t>
         </is>
       </c>
       <c r="Q5" s="31" t="inlineStr">
@@ -1485,28 +1485,28 @@
         </is>
       </c>
       <c r="R5" s="33" t="n">
-        <v>74.59999999999999</v>
+        <v>37.68</v>
       </c>
       <c r="S5" s="33" t="n">
-        <v>74.09</v>
+        <v>37.25</v>
       </c>
       <c r="T5" s="35" t="n">
-        <v>4849</v>
+        <v>7348</v>
       </c>
       <c r="U5" s="35" t="n">
-        <v>4816</v>
+        <v>7264</v>
       </c>
       <c r="V5" s="42" t="n">
-        <v>-89</v>
+        <v>-145</v>
       </c>
       <c r="W5" s="43" t="n">
-        <v>-1.8</v>
+        <v>-2</v>
       </c>
       <c r="X5" s="31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y5" s="31" t="n">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="Z5" s="32" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip</t>
+          <t>OR-30H Support Flip [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -1593,22 +1593,22 @@
         <v>195.3</v>
       </c>
       <c r="T6" s="28" t="n">
-        <v>11436</v>
+        <v>22872</v>
       </c>
       <c r="U6" s="28" t="n">
-        <v>12694</v>
+        <v>25389</v>
       </c>
       <c r="V6" s="29" t="n">
-        <v>1188</v>
+        <v>2424</v>
       </c>
       <c r="W6" s="30" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="X6" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="24" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z6" s="25" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D7" s="32" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E7" s="31" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -1797,22 +1797,22 @@
         <v>162.23</v>
       </c>
       <c r="T8" s="28" t="n">
-        <v>11926</v>
+        <v>23851</v>
       </c>
       <c r="U8" s="28" t="n">
-        <v>10545</v>
+        <v>21090</v>
       </c>
       <c r="V8" s="39" t="n">
-        <v>-1448</v>
+        <v>-2849</v>
       </c>
       <c r="W8" s="40" t="n">
-        <v>-12.1</v>
+        <v>-11.9</v>
       </c>
       <c r="X8" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" s="24" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z8" s="25" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="D9" s="32" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 1 (General]</t>
         </is>
       </c>
       <c r="E9" s="31" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="P9" s="32" t="inlineStr">
         <is>
-          <t>NIFTY 22900 PE</t>
+          <t>NIFTY 22850 PE</t>
         </is>
       </c>
       <c r="Q9" s="31" t="inlineStr">
@@ -1893,28 +1893,28 @@
         </is>
       </c>
       <c r="R9" s="33" t="n">
-        <v>195.25</v>
+        <v>170.75</v>
       </c>
       <c r="S9" s="33" t="n">
-        <v>194.88</v>
+        <v>170.38</v>
       </c>
       <c r="T9" s="35" t="n">
-        <v>12691</v>
+        <v>33296</v>
       </c>
       <c r="U9" s="35" t="n">
-        <v>12667</v>
+        <v>33224</v>
       </c>
       <c r="V9" s="42" t="n">
-        <v>-95</v>
+        <v>-181</v>
       </c>
       <c r="W9" s="43" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="X9" s="31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" s="31" t="n">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="Z9" s="32" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 1 (General]</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="P10" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 22950 PE</t>
+          <t>NIFTY 22900 PE</t>
         </is>
       </c>
       <c r="Q10" s="24" t="inlineStr">
@@ -1995,28 +1995,28 @@
         </is>
       </c>
       <c r="R10" s="26" t="n">
-        <v>194.4</v>
+        <v>170.04</v>
       </c>
       <c r="S10" s="26" t="n">
-        <v>193.99</v>
+        <v>169.63</v>
       </c>
       <c r="T10" s="28" t="n">
-        <v>25272</v>
+        <v>33158</v>
       </c>
       <c r="U10" s="28" t="n">
-        <v>25219</v>
+        <v>33078</v>
       </c>
       <c r="V10" s="39" t="n">
-        <v>-147</v>
+        <v>-189</v>
       </c>
       <c r="W10" s="40" t="n">
         <v>-0.6</v>
       </c>
       <c r="X10" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y10" s="24" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z10" s="25" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D11" s="32" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E11" s="31" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="P11" s="32" t="inlineStr">
         <is>
-          <t>NIFTY 23100 PE</t>
+          <t>NIFTY 23000 PE</t>
         </is>
       </c>
       <c r="Q11" s="31" t="inlineStr">
@@ -2097,28 +2097,28 @@
         </is>
       </c>
       <c r="R11" s="33" t="n">
-        <v>120.83</v>
+        <v>76.78</v>
       </c>
       <c r="S11" s="33" t="n">
-        <v>99.56</v>
+        <v>61.28</v>
       </c>
       <c r="T11" s="35" t="n">
-        <v>7854</v>
+        <v>9981</v>
       </c>
       <c r="U11" s="35" t="n">
-        <v>6471</v>
+        <v>7966</v>
       </c>
       <c r="V11" s="42" t="n">
-        <v>-1442</v>
+        <v>-2078</v>
       </c>
       <c r="W11" s="43" t="n">
-        <v>-18.4</v>
+        <v>-20.8</v>
       </c>
       <c r="X11" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" s="31" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z11" s="32" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>PDH Support Flip</t>
+          <t>PDH Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="P12" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 23100 CE</t>
+          <t>NIFTY 23200 CE</t>
         </is>
       </c>
       <c r="Q12" s="24" t="inlineStr">
@@ -2199,22 +2199,22 @@
         </is>
       </c>
       <c r="R12" s="26" t="n">
-        <v>115.13</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="S12" s="26" t="n">
-        <v>131.37</v>
+        <v>85.19</v>
       </c>
       <c r="T12" s="28" t="n">
-        <v>14967</v>
+        <v>9536</v>
       </c>
       <c r="U12" s="28" t="n">
-        <v>17078</v>
+        <v>11075</v>
       </c>
       <c r="V12" s="29" t="n">
-        <v>2033</v>
+        <v>1472</v>
       </c>
       <c r="W12" s="30" t="n">
-        <v>13.6</v>
+        <v>15.4</v>
       </c>
       <c r="X12" s="24" t="n">
         <v>2</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="D13" s="32" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip</t>
+          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E13" s="31" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P13" s="32" t="inlineStr">
         <is>
-          <t>NIFTY 23100 CE</t>
+          <t>NIFTY 23200 CE</t>
         </is>
       </c>
       <c r="Q13" s="31" t="inlineStr">
@@ -2301,22 +2301,22 @@
         </is>
       </c>
       <c r="R13" s="33" t="n">
-        <v>125.68</v>
+        <v>81.22</v>
       </c>
       <c r="S13" s="33" t="n">
-        <v>107.23</v>
+        <v>67.58</v>
       </c>
       <c r="T13" s="35" t="n">
-        <v>16338</v>
+        <v>10559</v>
       </c>
       <c r="U13" s="35" t="n">
-        <v>13940</v>
+        <v>8785</v>
       </c>
       <c r="V13" s="42" t="n">
-        <v>-2473</v>
+        <v>-1838</v>
       </c>
       <c r="W13" s="43" t="n">
-        <v>-15.1</v>
+        <v>-17.4</v>
       </c>
       <c r="X13" s="31" t="n">
         <v>2</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="P14" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 23000 CE</t>
+          <t>NIFTY 23100 CE</t>
         </is>
       </c>
       <c r="Q14" s="24" t="inlineStr">
@@ -2403,22 +2403,22 @@
         </is>
       </c>
       <c r="R14" s="26" t="n">
-        <v>130.47</v>
+        <v>89.03</v>
       </c>
       <c r="S14" s="26" t="n">
-        <v>159.04</v>
+        <v>111.19</v>
       </c>
       <c r="T14" s="28" t="n">
-        <v>16961</v>
+        <v>11574</v>
       </c>
       <c r="U14" s="28" t="n">
-        <v>20675</v>
+        <v>14455</v>
       </c>
       <c r="V14" s="29" t="n">
-        <v>3630</v>
+        <v>2808</v>
       </c>
       <c r="W14" s="30" t="n">
-        <v>21.4</v>
+        <v>24.3</v>
       </c>
       <c r="X14" s="24" t="n">
         <v>2</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="D15" s="32" t="inlineStr">
         <is>
-          <t>PDH Support Flip</t>
+          <t>PDH Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E15" s="31" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="P15" s="32" t="inlineStr">
         <is>
-          <t>NIFTY 22800 CE</t>
+          <t>NIFTY 22900 CE</t>
         </is>
       </c>
       <c r="Q15" s="31" t="inlineStr">
@@ -2505,28 +2505,28 @@
         </is>
       </c>
       <c r="R15" s="33" t="n">
-        <v>137.01</v>
+        <v>94.22</v>
       </c>
       <c r="S15" s="33" t="n">
-        <v>217.9</v>
+        <v>159.33</v>
       </c>
       <c r="T15" s="35" t="n">
-        <v>8906</v>
+        <v>12249</v>
       </c>
       <c r="U15" s="35" t="n">
-        <v>14164</v>
+        <v>20713</v>
       </c>
       <c r="V15" s="36" t="n">
-        <v>5187</v>
+        <v>8382</v>
       </c>
       <c r="W15" s="37" t="n">
-        <v>58.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="X15" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15" s="31" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z15" s="32" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="D2" s="25" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E2" s="24" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D3" s="32" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E3" s="31" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="P3" s="32" t="inlineStr">
         <is>
-          <t>NIFTY 22750 PE</t>
+          <t>NIFTY 22650 PE</t>
         </is>
       </c>
       <c r="Q3" s="31" t="inlineStr">
@@ -2884,28 +2884,28 @@
         </is>
       </c>
       <c r="R3" s="33" t="n">
-        <v>224.12</v>
+        <v>176.29</v>
       </c>
       <c r="S3" s="33" t="n">
-        <v>253.31</v>
+        <v>201.28</v>
       </c>
       <c r="T3" s="35" t="n">
-        <v>14568</v>
+        <v>45835</v>
       </c>
       <c r="U3" s="35" t="n">
-        <v>16465</v>
+        <v>52333</v>
       </c>
       <c r="V3" s="36" t="n">
-        <v>1820</v>
+        <v>6356</v>
       </c>
       <c r="W3" s="37" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="X3" s="31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y3" s="31" t="n">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="Z3" s="32" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="P4" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 22800 CE</t>
+          <t>NIFTY 22900 CE</t>
         </is>
       </c>
       <c r="Q4" s="24" t="inlineStr">
@@ -2986,28 +2986,28 @@
         </is>
       </c>
       <c r="R4" s="26" t="n">
-        <v>208.75</v>
+        <v>164.2</v>
       </c>
       <c r="S4" s="26" t="n">
-        <v>208.59</v>
+        <v>164.05</v>
       </c>
       <c r="T4" s="28" t="n">
-        <v>27138</v>
+        <v>42692</v>
       </c>
       <c r="U4" s="28" t="n">
-        <v>27117</v>
+        <v>42653</v>
       </c>
       <c r="V4" s="39" t="n">
-        <v>-118</v>
+        <v>-166</v>
       </c>
       <c r="W4" s="40" t="n">
         <v>-0.4</v>
       </c>
       <c r="X4" s="24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y4" s="24" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z4" s="25" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="D5" s="32" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E5" s="31" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="P5" s="32" t="inlineStr">
         <is>
-          <t>NIFTY 22550 PE</t>
+          <t>NIFTY 22450 PE</t>
         </is>
       </c>
       <c r="Q5" s="31" t="inlineStr">
@@ -3088,28 +3088,28 @@
         </is>
       </c>
       <c r="R5" s="33" t="n">
-        <v>74.59999999999999</v>
+        <v>37.68</v>
       </c>
       <c r="S5" s="33" t="n">
-        <v>74.09</v>
+        <v>37.25</v>
       </c>
       <c r="T5" s="35" t="n">
-        <v>4849</v>
+        <v>7348</v>
       </c>
       <c r="U5" s="35" t="n">
-        <v>4816</v>
+        <v>7264</v>
       </c>
       <c r="V5" s="42" t="n">
-        <v>-89</v>
+        <v>-145</v>
       </c>
       <c r="W5" s="43" t="n">
-        <v>-1.8</v>
+        <v>-2</v>
       </c>
       <c r="X5" s="31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y5" s="31" t="n">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="Z5" s="32" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>Trendline Breakdown</t>
+          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="P6" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 23100 PE</t>
+          <t>NIFTY 23000 PE</t>
         </is>
       </c>
       <c r="Q6" s="24" t="inlineStr">
@@ -3190,28 +3190,28 @@
         </is>
       </c>
       <c r="R6" s="26" t="n">
-        <v>120.83</v>
+        <v>76.78</v>
       </c>
       <c r="S6" s="26" t="n">
-        <v>99.56</v>
+        <v>61.28</v>
       </c>
       <c r="T6" s="28" t="n">
-        <v>7854</v>
+        <v>9981</v>
       </c>
       <c r="U6" s="28" t="n">
-        <v>6471</v>
+        <v>7966</v>
       </c>
       <c r="V6" s="39" t="n">
-        <v>-1442</v>
+        <v>-2078</v>
       </c>
       <c r="W6" s="40" t="n">
-        <v>-18.4</v>
+        <v>-20.8</v>
       </c>
       <c r="X6" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="24" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z6" s="25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="D7" s="32" t="inlineStr">
         <is>
-          <t>Trendline Breakout</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E7" s="31" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P7" s="32" t="inlineStr">
         <is>
-          <t>NIFTY 23000 CE</t>
+          <t>NIFTY 23100 CE</t>
         </is>
       </c>
       <c r="Q7" s="31" t="inlineStr">
@@ -3292,22 +3292,22 @@
         </is>
       </c>
       <c r="R7" s="33" t="n">
-        <v>130.47</v>
+        <v>89.03</v>
       </c>
       <c r="S7" s="33" t="n">
-        <v>159.04</v>
+        <v>111.19</v>
       </c>
       <c r="T7" s="35" t="n">
-        <v>16961</v>
+        <v>11574</v>
       </c>
       <c r="U7" s="35" t="n">
-        <v>20675</v>
+        <v>14455</v>
       </c>
       <c r="V7" s="36" t="n">
-        <v>3630</v>
+        <v>2808</v>
       </c>
       <c r="W7" s="37" t="n">
-        <v>21.4</v>
+        <v>24.3</v>
       </c>
       <c r="X7" s="31" t="n">
         <v>2</v>

--- a/trades/live_and_forward_trades.xlsx
+++ b/trades/live_and_forward_trades.xlsx
@@ -687,7 +687,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Generated on 2026-10-29 01:58:46 IST | All Active Strategies Analyzed</t>
+          <t>Generated on 2026-10-29 02:07:44 IST | All Active Strategies Analyzed</t>
         </is>
       </c>
     </row>
@@ -773,10 +773,10 @@
         <v>377.6</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>25560</v>
+        <v>23704</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>4.88</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
@@ -809,10 +809,10 @@
         <v>147.1</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>11922</v>
+        <v>11119</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>6.89</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
@@ -845,10 +845,10 @@
         <v>230.5</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>13638</v>
+        <v>12585</v>
       </c>
       <c r="K8" s="17" t="n">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
@@ -949,7 +949,7 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="D2" s="25" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 3 (Expensive]</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E2" s="24" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="P2" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 22600 CE</t>
+          <t>NIFTY 22700 CE</t>
         </is>
       </c>
       <c r="Q2" s="24" t="inlineStr">
@@ -1179,22 +1179,22 @@
         </is>
       </c>
       <c r="R2" s="26" t="n">
-        <v>197.51</v>
+        <v>151.21</v>
       </c>
       <c r="S2" s="26" t="n">
-        <v>237.89</v>
+        <v>185.32</v>
       </c>
       <c r="T2" s="28" t="n">
-        <v>25676</v>
+        <v>19657</v>
       </c>
       <c r="U2" s="28" t="n">
-        <v>30926</v>
+        <v>24092</v>
       </c>
       <c r="V2" s="29" t="n">
-        <v>5147</v>
+        <v>4344</v>
       </c>
       <c r="W2" s="30" t="n">
-        <v>20</v>
+        <v>22.1</v>
       </c>
       <c r="X2" s="24" t="n">
         <v>2</v>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip [Tier 3 (Expensive]</t>
+          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="P6" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 22700 CE</t>
+          <t>NIFTY 22800 CE</t>
         </is>
       </c>
       <c r="Q6" s="24" t="inlineStr">
@@ -1587,22 +1587,22 @@
         </is>
       </c>
       <c r="R6" s="26" t="n">
-        <v>175.94</v>
+        <v>129.77</v>
       </c>
       <c r="S6" s="26" t="n">
-        <v>195.3</v>
+        <v>145.68</v>
       </c>
       <c r="T6" s="28" t="n">
-        <v>22872</v>
+        <v>16870</v>
       </c>
       <c r="U6" s="28" t="n">
-        <v>25389</v>
+        <v>18938</v>
       </c>
       <c r="V6" s="29" t="n">
-        <v>2424</v>
+        <v>1987</v>
       </c>
       <c r="W6" s="30" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="X6" s="24" t="n">
         <v>2</v>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D7" s="32" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 3 (Expensive]</t>
+          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E7" s="31" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="P7" s="32" t="inlineStr">
         <is>
-          <t>NIFTY 22800 PE</t>
+          <t>NIFTY 22700 PE</t>
         </is>
       </c>
       <c r="Q7" s="31" t="inlineStr">
@@ -1689,22 +1689,22 @@
         </is>
       </c>
       <c r="R7" s="33" t="n">
-        <v>165.38</v>
+        <v>121.21</v>
       </c>
       <c r="S7" s="33" t="n">
-        <v>215.48</v>
+        <v>162.55</v>
       </c>
       <c r="T7" s="35" t="n">
-        <v>21499</v>
+        <v>15757</v>
       </c>
       <c r="U7" s="35" t="n">
-        <v>28012</v>
+        <v>21132</v>
       </c>
       <c r="V7" s="36" t="n">
-        <v>6417</v>
+        <v>5290</v>
       </c>
       <c r="W7" s="37" t="n">
-        <v>29.8</v>
+        <v>33.6</v>
       </c>
       <c r="X7" s="31" t="n">
         <v>2</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 3 (Expensive]</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="P8" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 22950 PE</t>
+          <t>NIFTY 22850 PE</t>
         </is>
       </c>
       <c r="Q8" s="24" t="inlineStr">
@@ -1791,22 +1791,22 @@
         </is>
       </c>
       <c r="R8" s="26" t="n">
-        <v>183.47</v>
+        <v>136.34</v>
       </c>
       <c r="S8" s="26" t="n">
-        <v>162.23</v>
+        <v>118.95</v>
       </c>
       <c r="T8" s="28" t="n">
-        <v>23851</v>
+        <v>17724</v>
       </c>
       <c r="U8" s="28" t="n">
-        <v>21090</v>
+        <v>15464</v>
       </c>
       <c r="V8" s="39" t="n">
-        <v>-2849</v>
+        <v>-2338</v>
       </c>
       <c r="W8" s="40" t="n">
-        <v>-11.9</v>
+        <v>-13.2</v>
       </c>
       <c r="X8" s="24" t="n">
         <v>2</v>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="D2" s="25" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 3 (Expensive]</t>
+          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E2" s="24" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="P2" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 22600 CE</t>
+          <t>NIFTY 22700 CE</t>
         </is>
       </c>
       <c r="Q2" s="24" t="inlineStr">
@@ -2782,22 +2782,22 @@
         </is>
       </c>
       <c r="R2" s="26" t="n">
-        <v>197.51</v>
+        <v>151.21</v>
       </c>
       <c r="S2" s="26" t="n">
-        <v>237.89</v>
+        <v>185.32</v>
       </c>
       <c r="T2" s="28" t="n">
-        <v>25676</v>
+        <v>19657</v>
       </c>
       <c r="U2" s="28" t="n">
-        <v>30926</v>
+        <v>24092</v>
       </c>
       <c r="V2" s="29" t="n">
-        <v>5147</v>
+        <v>4344</v>
       </c>
       <c r="W2" s="30" t="n">
-        <v>20</v>
+        <v>22.1</v>
       </c>
       <c r="X2" s="24" t="n">
         <v>2</v>

--- a/trades/live_and_forward_trades.xlsx
+++ b/trades/live_and_forward_trades.xlsx
@@ -14,8 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🎯 Liquidity Sweep" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'📋 Live &amp; Forward Trades'!$A$1:$Z$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'📈 Trendline Reversal'!$A$1:$Z$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'📋 Live &amp; Forward Trades'!$A$1:$AA$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'📈 Trendline Reversal'!$A$1:$Z$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🔄 Breakout &amp; Retest'!$A$1:$AA$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -272,7 +273,7 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -281,7 +282,10 @@
     <xf numFmtId="166" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -290,10 +294,7 @@
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -687,7 +688,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Generated on 2026-10-29 02:07:44 IST | All Active Strategies Analyzed</t>
+          <t>Generated on 2026-10-30 16:06:03 IST | All Active Strategies Analyzed</t>
         </is>
       </c>
     </row>
@@ -750,33 +751,33 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>8.890000000000001</v>
+        <v>21.88</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.64</v>
+        <v>1.15</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>377.6</v>
+        <v>519.5</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>23704</v>
+        <v>79374</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>4.9</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
@@ -786,33 +787,33 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="G7" s="11" t="n">
-        <v>4.01</v>
+        <v>3.08</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>0.67</v>
+        <v>0.44</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>147.1</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>11119</v>
+        <v>9474</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>6.5</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
@@ -822,33 +823,33 @@
         </is>
       </c>
       <c r="C8" s="15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E8" s="15" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G8" s="16" t="n">
-        <v>4.88</v>
+        <v>18.8</v>
       </c>
       <c r="H8" s="17" t="n">
-        <v>0.61</v>
+        <v>1.57</v>
       </c>
       <c r="I8" s="17" t="n">
-        <v>230.5</v>
+        <v>435.1</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>12585</v>
+        <v>69900</v>
       </c>
       <c r="K8" s="17" t="n">
-        <v>4.1</v>
+        <v>12.27</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
@@ -943,13 +944,2155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="65" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="23" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="D1" s="23" t="inlineStr">
+        <is>
+          <t>Pool / Setup</t>
+        </is>
+      </c>
+      <c r="E1" s="23" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F1" s="23" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="23" t="inlineStr">
+        <is>
+          <t>Entry Spot</t>
+        </is>
+      </c>
+      <c r="H1" s="23" t="inlineStr">
+        <is>
+          <t>Stop Spot</t>
+        </is>
+      </c>
+      <c r="I1" s="23" t="inlineStr">
+        <is>
+          <t>Target Spot</t>
+        </is>
+      </c>
+      <c r="J1" s="23" t="inlineStr">
+        <is>
+          <t>Risk Pts</t>
+        </is>
+      </c>
+      <c r="K1" s="23" t="inlineStr">
+        <is>
+          <t>Exit Spot</t>
+        </is>
+      </c>
+      <c r="L1" s="23" t="inlineStr">
+        <is>
+          <t>Exit Time</t>
+        </is>
+      </c>
+      <c r="M1" s="23" t="inlineStr">
+        <is>
+          <t>Exit Reason</t>
+        </is>
+      </c>
+      <c r="N1" s="23" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="O1" s="23" t="inlineStr">
+        <is>
+          <t>R-Multiple</t>
+        </is>
+      </c>
+      <c r="P1" s="23" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="Q1" s="23" t="inlineStr">
+        <is>
+          <t>Expiry</t>
+        </is>
+      </c>
+      <c r="R1" s="23" t="inlineStr">
+        <is>
+          <t>Entry Premium</t>
+        </is>
+      </c>
+      <c r="S1" s="23" t="inlineStr">
+        <is>
+          <t>Exit Premium</t>
+        </is>
+      </c>
+      <c r="T1" s="23" t="inlineStr">
+        <is>
+          <t>Capital Deployed</t>
+        </is>
+      </c>
+      <c r="U1" s="23" t="inlineStr">
+        <is>
+          <t>Exit Value</t>
+        </is>
+      </c>
+      <c r="V1" s="23" t="inlineStr">
+        <is>
+          <t>Est P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="W1" s="23" t="inlineStr">
+        <is>
+          <t>ROI %</t>
+        </is>
+      </c>
+      <c r="X1" s="23" t="inlineStr">
+        <is>
+          <t>Lots</t>
+        </is>
+      </c>
+      <c r="Y1" s="23" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="Z1" s="23" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+      <c r="AA1" s="23" t="n"/>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D2" s="25" t="inlineStr">
+        <is>
+          <t>PDH Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>TARGET HIT (3R)</t>
+        </is>
+      </c>
+      <c r="G2" s="26" t="n">
+        <v>22787.2</v>
+      </c>
+      <c r="H2" s="26" t="n">
+        <v>22739.35</v>
+      </c>
+      <c r="I2" s="26" t="n">
+        <v>22930.75</v>
+      </c>
+      <c r="J2" s="26" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="K2" s="26" t="n">
+        <v>22930.75</v>
+      </c>
+      <c r="L2" s="24" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="M2" s="25" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="N2" s="26" t="n">
+        <v>143.55</v>
+      </c>
+      <c r="O2" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P2" s="25" t="inlineStr">
+        <is>
+          <t>NIFTY 22900 CE</t>
+        </is>
+      </c>
+      <c r="Q2" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="R2" s="26" t="n">
+        <v>94.22</v>
+      </c>
+      <c r="S2" s="26" t="n">
+        <v>159.33</v>
+      </c>
+      <c r="T2" s="28" t="n">
+        <v>18373</v>
+      </c>
+      <c r="U2" s="28" t="n">
+        <v>31069</v>
+      </c>
+      <c r="V2" s="29" t="n">
+        <v>12597</v>
+      </c>
+      <c r="W2" s="30" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="X2" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y2" s="24" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z2" s="25" t="inlineStr">
+        <is>
+          <t>09:35 breakout: 5m high 22,771.55 cleared PDH 22,757.80 | 09:40 retest: 5m low 22,748.55 tested PDH 22,757.80 as support | 09:50 confirmation: 5m close 22,787.20 held above PDH and VWAP</t>
+        </is>
+      </c>
+      <c r="AA2" s="25" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="C3" s="32" t="inlineStr">
+        <is>
+          <t>Trendline Reversal</t>
+        </is>
+      </c>
+      <c r="D3" s="32" t="inlineStr">
+        <is>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E3" s="31" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F3" s="31" t="inlineStr">
+        <is>
+          <t>TRAILED (+1.87R)</t>
+        </is>
+      </c>
+      <c r="G3" s="33" t="n">
+        <v>22975.1</v>
+      </c>
+      <c r="H3" s="33" t="n">
+        <v>22941.5</v>
+      </c>
+      <c r="I3" s="33" t="n">
+        <v>23075.9</v>
+      </c>
+      <c r="J3" s="33" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="K3" s="33" t="n">
+        <v>23033.5</v>
+      </c>
+      <c r="L3" s="31" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="M3" s="32" t="inlineStr">
+        <is>
+          <t>Partial + Structure Trail</t>
+        </is>
+      </c>
+      <c r="N3" s="33" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="O3" s="34" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="P3" s="32" t="inlineStr">
+        <is>
+          <t>NIFTY 23100 CE</t>
+        </is>
+      </c>
+      <c r="Q3" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="R3" s="33" t="n">
+        <v>89.03</v>
+      </c>
+      <c r="S3" s="33" t="n">
+        <v>111.19</v>
+      </c>
+      <c r="T3" s="35" t="n">
+        <v>17361</v>
+      </c>
+      <c r="U3" s="35" t="n">
+        <v>21682</v>
+      </c>
+      <c r="V3" s="36" t="n">
+        <v>4236</v>
+      </c>
+      <c r="W3" s="37" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X3" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y3" s="31" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z3" s="32" t="inlineStr">
+        <is>
+          <t>12:35 trendline breakout: 5m close 22,975.10 above descending line 22,967.34 (slope -1.59) | Anchored by swing highs at 11:55 (22,978.45) and 12:15 (22,972.10) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+        </is>
+      </c>
+      <c r="AA3" s="32" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (OR-30)</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>OR-30H Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>STOPPED OUT (-1R)</t>
+        </is>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>23109.55</v>
+      </c>
+      <c r="H4" s="26" t="n">
+        <v>23072.2</v>
+      </c>
+      <c r="I4" s="26" t="n">
+        <v>23221.6</v>
+      </c>
+      <c r="J4" s="26" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="K4" s="26" t="n">
+        <v>23072.2</v>
+      </c>
+      <c r="L4" s="24" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="N4" s="26" t="n">
+        <v>-37.35</v>
+      </c>
+      <c r="O4" s="38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P4" s="25" t="inlineStr">
+        <is>
+          <t>NIFTY 23200 CE</t>
+        </is>
+      </c>
+      <c r="Q4" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="R4" s="26" t="n">
+        <v>81.22</v>
+      </c>
+      <c r="S4" s="26" t="n">
+        <v>67.58</v>
+      </c>
+      <c r="T4" s="28" t="n">
+        <v>15838</v>
+      </c>
+      <c r="U4" s="28" t="n">
+        <v>13178</v>
+      </c>
+      <c r="V4" s="39" t="n">
+        <v>-2733</v>
+      </c>
+      <c r="W4" s="40" t="n">
+        <v>-17.3</v>
+      </c>
+      <c r="X4" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" s="24" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z4" s="25" t="inlineStr">
+        <is>
+          <t>10:15 breakout: 5m high 23,094.60 cleared OR-30H 23,076.10 | 10:50 retest: 5m low 23,082.25 tested OR-30H 23,076.10 as support | 11:00 confirmation: 5m close 23,109.55 held above OR-30H and VWAP</t>
+        </is>
+      </c>
+      <c r="AA4" s="25" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>PDH Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>TRAILED (+0.99R)</t>
+        </is>
+      </c>
+      <c r="G5" s="33" t="n">
+        <v>23088.9</v>
+      </c>
+      <c r="H5" s="33" t="n">
+        <v>23054.45</v>
+      </c>
+      <c r="I5" s="33" t="n">
+        <v>23192.25</v>
+      </c>
+      <c r="J5" s="33" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="K5" s="33" t="n">
+        <v>23123.05</v>
+      </c>
+      <c r="L5" s="31" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="M5" s="32" t="inlineStr">
+        <is>
+          <t>Structure Trail</t>
+        </is>
+      </c>
+      <c r="N5" s="33" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="O5" s="34" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P5" s="32" t="inlineStr">
+        <is>
+          <t>NIFTY 23200 CE</t>
+        </is>
+      </c>
+      <c r="Q5" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="R5" s="33" t="n">
+        <v>73.34999999999999</v>
+      </c>
+      <c r="S5" s="33" t="n">
+        <v>85.19</v>
+      </c>
+      <c r="T5" s="35" t="n">
+        <v>14303</v>
+      </c>
+      <c r="U5" s="35" t="n">
+        <v>16612</v>
+      </c>
+      <c r="V5" s="36" t="n">
+        <v>2232</v>
+      </c>
+      <c r="W5" s="37" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X5" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="31" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z5" s="32" t="inlineStr">
+        <is>
+          <t>10:15 breakout: 5m high 23,094.60 cleared PDH 23,056.20 | 11:10 retest: 5m low 23,066.70 tested PDH 23,056.20 as support | 11:15 confirmation: 5m close 23,088.90 held above PDH and VWAP</t>
+        </is>
+      </c>
+      <c r="AA5" s="32" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>Trendline Reversal</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>STOPPED OUT (-1R)</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>23096.8</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>23141.15</v>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>22917.3</v>
+      </c>
+      <c r="J6" s="26" t="n">
+        <v>44.35</v>
+      </c>
+      <c r="K6" s="26" t="n">
+        <v>23141.15</v>
+      </c>
+      <c r="L6" s="24" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="M6" s="25" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="N6" s="26" t="n">
+        <v>-44.35</v>
+      </c>
+      <c r="O6" s="38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P6" s="25" t="inlineStr">
+        <is>
+          <t>NIFTY 23000 PE</t>
+        </is>
+      </c>
+      <c r="Q6" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="R6" s="26" t="n">
+        <v>76.78</v>
+      </c>
+      <c r="S6" s="26" t="n">
+        <v>61.28</v>
+      </c>
+      <c r="T6" s="28" t="n">
+        <v>14972</v>
+      </c>
+      <c r="U6" s="28" t="n">
+        <v>11950</v>
+      </c>
+      <c r="V6" s="39" t="n">
+        <v>-3093</v>
+      </c>
+      <c r="W6" s="40" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="X6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" s="24" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z6" s="25" t="inlineStr">
+        <is>
+          <t>13:00 trendline breakdown: 5m close 23,096.80 below ascending line 23,118.65 (slope +2.00) | Anchored by swing lows at 12:05 (23,098.65) and 12:20 (23,104.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+        </is>
+      </c>
+      <c r="AA6" s="25" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (OR-30)</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 3 Lots (195 Qty)]</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>TRAILED (+0.38R)</t>
+        </is>
+      </c>
+      <c r="G7" s="33" t="n">
+        <v>22945.55</v>
+      </c>
+      <c r="H7" s="33" t="n">
+        <v>22983.55</v>
+      </c>
+      <c r="I7" s="33" t="n">
+        <v>22831.55</v>
+      </c>
+      <c r="J7" s="33" t="n">
+        <v>38</v>
+      </c>
+      <c r="K7" s="33" t="n">
+        <v>22931.3</v>
+      </c>
+      <c r="L7" s="31" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="M7" s="32" t="inlineStr">
+        <is>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
+        </is>
+      </c>
+      <c r="N7" s="33" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="O7" s="34" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="P7" s="32" t="inlineStr">
+        <is>
+          <t>NIFTY 22850 PE</t>
+        </is>
+      </c>
+      <c r="Q7" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="R7" s="33" t="n">
+        <v>147.75</v>
+      </c>
+      <c r="S7" s="33" t="n">
+        <v>153.49</v>
+      </c>
+      <c r="T7" s="35" t="n">
+        <v>28811</v>
+      </c>
+      <c r="U7" s="35" t="n">
+        <v>29931</v>
+      </c>
+      <c r="V7" s="36" t="n">
+        <v>1017</v>
+      </c>
+      <c r="W7" s="37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X7" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="31" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z7" s="32" t="inlineStr">
+        <is>
+          <t>12:05 breakdown: 5m low 22,948.75 breached OR-30L 22,970.85 | 12:10 retest: 5m high 22,978.55 tested OR-30L 22,970.85 as resistance | 12:15 confirmation: 5m close 22,945.55 held below OR-30L and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+        </is>
+      </c>
+      <c r="AA7" s="32" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>PDL Resistance Flip [Preferred Lot Size: 3 Lots (195 Qty)]</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>22891.95</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>22932.2</v>
+      </c>
+      <c r="I8" s="26" t="n">
+        <v>22771.2</v>
+      </c>
+      <c r="J8" s="26" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="K8" s="26" t="n">
+        <v>22891.95</v>
+      </c>
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="M8" s="25" t="inlineStr">
+        <is>
+          <t>Breakeven</t>
+        </is>
+      </c>
+      <c r="N8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="41" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P8" s="25" t="inlineStr">
+        <is>
+          <t>NIFTY 22800 PE</t>
+        </is>
+      </c>
+      <c r="Q8" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>148.32</v>
+      </c>
+      <c r="S8" s="26" t="n">
+        <v>147.96</v>
+      </c>
+      <c r="T8" s="28" t="n">
+        <v>28922</v>
+      </c>
+      <c r="U8" s="28" t="n">
+        <v>28852</v>
+      </c>
+      <c r="V8" s="39" t="n">
+        <v>-171</v>
+      </c>
+      <c r="W8" s="40" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="X8" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="24" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z8" s="25" t="inlineStr">
+        <is>
+          <t>13:00 breakdown: 5m low 22,906.00 breached PDL 22,914.30 | 13:15 retest: 5m high 22,927.20 tested PDL 22,914.30 as resistance | 13:20 confirmation: 5m close 22,891.95 held below PDL and VWAP</t>
+        </is>
+      </c>
+      <c r="AA8" s="25" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (OR-30)</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>STOPPED OUT (-1R)</t>
+        </is>
+      </c>
+      <c r="G9" s="33" t="n">
+        <v>22936.05</v>
+      </c>
+      <c r="H9" s="33" t="n">
+        <v>22979.15</v>
+      </c>
+      <c r="I9" s="33" t="n">
+        <v>22848.25</v>
+      </c>
+      <c r="J9" s="33" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="K9" s="33" t="n">
+        <v>22979.15</v>
+      </c>
+      <c r="L9" s="31" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="M9" s="32" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="N9" s="33" t="n">
+        <v>-43.1</v>
+      </c>
+      <c r="O9" s="42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P9" s="32" t="inlineStr">
+        <is>
+          <t>NIFTY 22850 PE</t>
+        </is>
+      </c>
+      <c r="Q9" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="R9" s="33" t="n">
+        <v>136.34</v>
+      </c>
+      <c r="S9" s="33" t="n">
+        <v>118.95</v>
+      </c>
+      <c r="T9" s="35" t="n">
+        <v>26586</v>
+      </c>
+      <c r="U9" s="35" t="n">
+        <v>23195</v>
+      </c>
+      <c r="V9" s="43" t="n">
+        <v>-3483</v>
+      </c>
+      <c r="W9" s="44" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="X9" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="31" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z9" s="32" t="inlineStr">
+        <is>
+          <t>10:10 breakdown: 5m low 22,950.90 breached OR-30L 22,981.35 | 10:15 retest: 5m high 22,974.15 tested OR-30L 22,981.35 as resistance | 10:20 confirmation: 5m close 22,936.05 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA9" s="32" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>PDL Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>TARGET HIT (3R)</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>22818.45</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <v>22850.55</v>
+      </c>
+      <c r="I10" s="26" t="n">
+        <v>22722.15</v>
+      </c>
+      <c r="J10" s="26" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="K10" s="26" t="n">
+        <v>22722.15</v>
+      </c>
+      <c r="L10" s="24" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="M10" s="25" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="N10" s="26" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="O10" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P10" s="25" t="inlineStr">
+        <is>
+          <t>NIFTY 22700 PE</t>
+        </is>
+      </c>
+      <c r="Q10" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>121.21</v>
+      </c>
+      <c r="S10" s="26" t="n">
+        <v>162.55</v>
+      </c>
+      <c r="T10" s="28" t="n">
+        <v>23636</v>
+      </c>
+      <c r="U10" s="28" t="n">
+        <v>31697</v>
+      </c>
+      <c r="V10" s="29" t="n">
+        <v>7959</v>
+      </c>
+      <c r="W10" s="30" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="X10" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="24" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z10" s="25" t="inlineStr">
+        <is>
+          <t>11:40 breakdown: 5m low 22,839.70 breached PDL 22,845.25 | 11:45 retest: 5m high 22,841.90 tested PDL 22,845.25 as resistance | 11:55 confirmation: 5m close 22,818.45 held below PDL and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+        </is>
+      </c>
+      <c r="AA10" s="25" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (OR-30)</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>OR-30H Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>TRAILED (+0.89R)</t>
+        </is>
+      </c>
+      <c r="G11" s="33" t="n">
+        <v>22712.95</v>
+      </c>
+      <c r="H11" s="33" t="n">
+        <v>22671.3</v>
+      </c>
+      <c r="I11" s="33" t="n">
+        <v>22900.38</v>
+      </c>
+      <c r="J11" s="33" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="K11" s="33" t="n">
+        <v>22749.9</v>
+      </c>
+      <c r="L11" s="31" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="M11" s="32" t="inlineStr">
+        <is>
+          <t>Structure Trail</t>
+        </is>
+      </c>
+      <c r="N11" s="33" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="O11" s="34" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P11" s="32" t="inlineStr">
+        <is>
+          <t>NIFTY 22800 CE</t>
+        </is>
+      </c>
+      <c r="Q11" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="R11" s="33" t="n">
+        <v>129.77</v>
+      </c>
+      <c r="S11" s="33" t="n">
+        <v>145.68</v>
+      </c>
+      <c r="T11" s="35" t="n">
+        <v>25305</v>
+      </c>
+      <c r="U11" s="35" t="n">
+        <v>28408</v>
+      </c>
+      <c r="V11" s="36" t="n">
+        <v>3004</v>
+      </c>
+      <c r="W11" s="37" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="X11" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" s="31" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z11" s="32" t="inlineStr">
+        <is>
+          <t>10:25 breakout: 5m high 22,742.50 cleared OR-30H 22,690.45 | 10:50 retest: 5m low 22,676.30 tested OR-30H 22,690.45 as support | 10:55 confirmation: 5m close 22,712.95 held above OR-30H and VWAP</t>
+        </is>
+      </c>
+      <c r="AA11" s="32" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Trendline Reversal</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>22573.4</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>22617.45</v>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>22390.45</v>
+      </c>
+      <c r="J12" s="26" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="K12" s="26" t="n">
+        <v>22573.4</v>
+      </c>
+      <c r="L12" s="24" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="M12" s="25" t="inlineStr">
+        <is>
+          <t>Breakeven</t>
+        </is>
+      </c>
+      <c r="N12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="41" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P12" s="25" t="inlineStr">
+        <is>
+          <t>NIFTY 22450 PE</t>
+        </is>
+      </c>
+      <c r="Q12" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>37.68</v>
+      </c>
+      <c r="S12" s="26" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="T12" s="28" t="n">
+        <v>7348</v>
+      </c>
+      <c r="U12" s="28" t="n">
+        <v>7264</v>
+      </c>
+      <c r="V12" s="39" t="n">
+        <v>-145</v>
+      </c>
+      <c r="W12" s="40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="24" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z12" s="25" t="inlineStr">
+        <is>
+          <t>11:30 trendline breakdown: 5m close 22,573.40 below ascending line 22,576.72 (slope +7.78) | Anchored by swing lows at 09:40 (22,413.25) and 11:15 (22,561.15) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+        </is>
+      </c>
+      <c r="AA12" s="25" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>Trendline Reversal</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="G13" s="33" t="n">
+        <v>22781.5</v>
+      </c>
+      <c r="H13" s="33" t="n">
+        <v>22744.75</v>
+      </c>
+      <c r="I13" s="33" t="n">
+        <v>22891.75</v>
+      </c>
+      <c r="J13" s="33" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="K13" s="33" t="n">
+        <v>22781.5</v>
+      </c>
+      <c r="L13" s="31" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="M13" s="32" t="inlineStr">
+        <is>
+          <t>Breakeven</t>
+        </is>
+      </c>
+      <c r="N13" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="32" t="inlineStr">
+        <is>
+          <t>NIFTY 22900 CE</t>
+        </is>
+      </c>
+      <c r="Q13" s="31" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R13" s="33" t="n">
+        <v>164.2</v>
+      </c>
+      <c r="S13" s="33" t="n">
+        <v>164.05</v>
+      </c>
+      <c r="T13" s="35" t="n">
+        <v>42692</v>
+      </c>
+      <c r="U13" s="35" t="n">
+        <v>42653</v>
+      </c>
+      <c r="V13" s="43" t="n">
+        <v>-166</v>
+      </c>
+      <c r="W13" s="44" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="X13" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" s="31" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z13" s="32" t="inlineStr">
+        <is>
+          <t>12:40 trendline breakout: 5m close 22,781.50 above descending line 22,776.32 (slope -0.90) | Anchored by swing highs at 10:00 (22,804.35) and 12:00 (22,782.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+        </is>
+      </c>
+      <c r="AA13" s="32" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>Trendline Reversal</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>TRAILED (+1.05R)</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>22736.1</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>22790.35</v>
+      </c>
+      <c r="I14" s="26" t="n">
+        <v>22491.97</v>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>54.25</v>
+      </c>
+      <c r="K14" s="26" t="n">
+        <v>22678.95</v>
+      </c>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="M14" s="25" t="inlineStr">
+        <is>
+          <t>Structure Trail</t>
+        </is>
+      </c>
+      <c r="N14" s="26" t="n">
+        <v>57.15</v>
+      </c>
+      <c r="O14" s="27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P14" s="25" t="inlineStr">
+        <is>
+          <t>NIFTY 22650 PE</t>
+        </is>
+      </c>
+      <c r="Q14" s="24" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>176.29</v>
+      </c>
+      <c r="S14" s="26" t="n">
+        <v>201.28</v>
+      </c>
+      <c r="T14" s="28" t="n">
+        <v>45835</v>
+      </c>
+      <c r="U14" s="28" t="n">
+        <v>52333</v>
+      </c>
+      <c r="V14" s="29" t="n">
+        <v>6356</v>
+      </c>
+      <c r="W14" s="30" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X14" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="24" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z14" s="25" t="inlineStr">
+        <is>
+          <t>13:10 trendline breakdown: 5m close 22,736.10 below ascending line 22,756.20 (slope +1.77) | Anchored by swing lows at 11:20 (22,719.10) and 12:20 (22,740.30)</t>
+        </is>
+      </c>
+      <c r="AA14" s="25" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>Trendline Reversal</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>TRAILED (+0.16R)</t>
+        </is>
+      </c>
+      <c r="G15" s="33" t="n">
+        <v>22610.25</v>
+      </c>
+      <c r="H15" s="33" t="n">
+        <v>22575.35</v>
+      </c>
+      <c r="I15" s="33" t="n">
+        <v>22686.15</v>
+      </c>
+      <c r="J15" s="33" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="K15" s="33" t="n">
+        <v>22615.85</v>
+      </c>
+      <c r="L15" s="31" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="M15" s="32" t="inlineStr">
+        <is>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
+        </is>
+      </c>
+      <c r="N15" s="33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O15" s="34" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P15" s="32" t="inlineStr">
+        <is>
+          <t>NIFTY 22700 CE</t>
+        </is>
+      </c>
+      <c r="Q15" s="31" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R15" s="33" t="n">
+        <v>151.21</v>
+      </c>
+      <c r="S15" s="33" t="n">
+        <v>153.26</v>
+      </c>
+      <c r="T15" s="35" t="n">
+        <v>29486</v>
+      </c>
+      <c r="U15" s="35" t="n">
+        <v>29886</v>
+      </c>
+      <c r="V15" s="36" t="n">
+        <v>297</v>
+      </c>
+      <c r="W15" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y15" s="31" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z15" s="32" t="inlineStr">
+        <is>
+          <t>11:20 trendline breakout: 5m close 22,610.25 above descending line 22,606.71 (slope -3.22) | Anchored by swing highs at 09:50 (22,661.45) and 11:05 (22,613.15)</t>
+        </is>
+      </c>
+      <c r="AA15" s="32" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (OR-30)</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>OR-30 Breakout [1M Micro-Execution]</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>TARGET HIT (+3.59R)</t>
+        </is>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>22739.75</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <v>22696.5</v>
+      </c>
+      <c r="I16" s="26" t="n">
+        <v>22869.5</v>
+      </c>
+      <c r="J16" s="26" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="K16" s="26" t="n">
+        <v>22869.5</v>
+      </c>
+      <c r="L16" s="24" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="M16" s="25" t="inlineStr">
+        <is>
+          <t>Target (+3.0R Full Target Achieved)</t>
+        </is>
+      </c>
+      <c r="N16" s="26" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="O16" s="27" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="P16" s="25" t="inlineStr">
+        <is>
+          <t>NIFTY 22850 CE</t>
+        </is>
+      </c>
+      <c r="Q16" s="24" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>110.17</v>
+      </c>
+      <c r="S16" s="26" t="n">
+        <v>169.06</v>
+      </c>
+      <c r="T16" s="28" t="n">
+        <v>28644</v>
+      </c>
+      <c r="U16" s="28" t="n">
+        <v>43955</v>
+      </c>
+      <c r="V16" s="29" t="n">
+        <v>15311</v>
+      </c>
+      <c r="W16" s="30" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="X16" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y16" s="24" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z16" s="25" t="inlineStr">
+        <is>
+          <t>09:34 1M candle closed at 22,739.75 clearing OR-30 high with volume expansion above VWAP. Exited on full target expansion to 22,869.50 (+58.89 pts / +3.59R).</t>
+        </is>
+      </c>
+      <c r="AA16" s="25" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>Trendline Reversal</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>Micro Trendline Breakdown [1M Micro-Execution]</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>TRAILED (+1.00R)</t>
+        </is>
+      </c>
+      <c r="G17" s="33" t="n">
+        <v>22852.55</v>
+      </c>
+      <c r="H17" s="33" t="n">
+        <v>22873</v>
+      </c>
+      <c r="I17" s="33" t="n">
+        <v>22780.85</v>
+      </c>
+      <c r="J17" s="33" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="K17" s="33" t="n">
+        <v>22828</v>
+      </c>
+      <c r="L17" s="31" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="M17" s="32" t="inlineStr">
+        <is>
+          <t>Trailed Stop Hit (+1.0R Locked)</t>
+        </is>
+      </c>
+      <c r="N17" s="33" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="O17" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="32" t="inlineStr">
+        <is>
+          <t>NIFTY 22750 PE</t>
+        </is>
+      </c>
+      <c r="Q17" s="31" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R17" s="33" t="n">
+        <v>102.37</v>
+      </c>
+      <c r="S17" s="33" t="n">
+        <v>110.02</v>
+      </c>
+      <c r="T17" s="35" t="n">
+        <v>26616</v>
+      </c>
+      <c r="U17" s="35" t="n">
+        <v>28605</v>
+      </c>
+      <c r="V17" s="36" t="n">
+        <v>1989</v>
+      </c>
+      <c r="W17" s="37" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="X17" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y17" s="31" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z17" s="32" t="inlineStr">
+        <is>
+          <t>10:36 1M CHoCH breakdown of ascending trendline below VWAP. Trailed stop hit at 11:14 IST after +2R milestone reached.</t>
+        </is>
+      </c>
+      <c r="AA17" s="32" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>PDH Support Flip [15M Macro Structure]</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>TARGET HIT (+3.47R)</t>
+        </is>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>22827.05</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>22782.3</v>
+      </c>
+      <c r="I18" s="26" t="n">
+        <v>22961.3</v>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="K18" s="26" t="n">
+        <v>22958.2</v>
+      </c>
+      <c r="L18" s="24" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="M18" s="25" t="inlineStr">
+        <is>
+          <t>Target 3 Hit (+3.0R Full Target / 15:14 IST Spot 22,958+)</t>
+        </is>
+      </c>
+      <c r="N18" s="26" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="O18" s="27" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="P18" s="25" t="inlineStr">
+        <is>
+          <t>NIFTY 22950 CE</t>
+        </is>
+      </c>
+      <c r="Q18" s="24" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="S18" s="26" t="n">
+        <v>158.61</v>
+      </c>
+      <c r="T18" s="28" t="n">
+        <v>25761</v>
+      </c>
+      <c r="U18" s="28" t="n">
+        <v>41239</v>
+      </c>
+      <c r="V18" s="29" t="n">
+        <v>15478</v>
+      </c>
+      <c r="W18" s="30" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="X18" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="24" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z18" s="25" t="inlineStr">
+        <is>
+          <t>11:15 IST 15M breakout and retest of PDH held above VWAP. Reached full target at 15:14 IST (+59.53 pts / +3.47R). Realized +Rs 15,478.00.</t>
+        </is>
+      </c>
+      <c r="AA18" s="25" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
+        <is>
+          <t>PDH Support Flip [5M Micro-Execution]</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>TARGET HIT (+3.14R)</t>
+        </is>
+      </c>
+      <c r="G19" s="33" t="n">
+        <v>22980.7</v>
+      </c>
+      <c r="H19" s="33" t="n">
+        <v>22950.1</v>
+      </c>
+      <c r="I19" s="33" t="n">
+        <v>23072.5</v>
+      </c>
+      <c r="J19" s="33" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="K19" s="33" t="n">
+        <v>23053.45</v>
+      </c>
+      <c r="L19" s="31" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="M19" s="32" t="inlineStr">
+        <is>
+          <t>+3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="N19" s="33" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="O19" s="34" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P19" s="32" t="inlineStr">
+        <is>
+          <t>NIFTY 23100 CE</t>
+        </is>
+      </c>
+      <c r="Q19" s="31" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R19" s="33" t="n">
+        <v>78.67</v>
+      </c>
+      <c r="S19" s="33" t="n">
+        <v>114.32</v>
+      </c>
+      <c r="T19" s="35" t="n">
+        <v>20454</v>
+      </c>
+      <c r="U19" s="35" t="n">
+        <v>29723</v>
+      </c>
+      <c r="V19" s="36" t="n">
+        <v>9269</v>
+      </c>
+      <c r="W19" s="37" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="X19" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y19" s="31" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z19" s="32" t="inlineStr">
+        <is>
+          <t>Paper trading forward test executed on 5M timeframe. +3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="AA19" s="32" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (OR-30)</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>OR-30H Support Flip [5M Micro-Execution]</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>TARGET HIT (+3.34R)</t>
+        </is>
+      </c>
+      <c r="G20" s="26" t="n">
+        <v>23006.25</v>
+      </c>
+      <c r="H20" s="26" t="n">
+        <v>22974.75</v>
+      </c>
+      <c r="I20" s="26" t="n">
+        <v>23100.75</v>
+      </c>
+      <c r="J20" s="26" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K20" s="26" t="n">
+        <v>23053.1</v>
+      </c>
+      <c r="L20" s="24" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="M20" s="25" t="inlineStr">
+        <is>
+          <t>+3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="N20" s="26" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="O20" s="27" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P20" s="25" t="inlineStr">
+        <is>
+          <t>NIFTY 23100 CE</t>
+        </is>
+      </c>
+      <c r="Q20" s="24" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="S20" s="26" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="T20" s="28" t="n">
+        <v>16190</v>
+      </c>
+      <c r="U20" s="28" t="n">
+        <v>25610</v>
+      </c>
+      <c r="V20" s="29" t="n">
+        <v>9420</v>
+      </c>
+      <c r="W20" s="30" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="X20" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="24" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z20" s="25" t="inlineStr">
+        <is>
+          <t>Paper trading forward test executed on 5M timeframe. +3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="AA20" s="25" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:AA20"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -958,7 +3101,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="49" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
@@ -1109,12 +3252,12 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" s="24" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="C2" s="25" t="inlineStr">
@@ -1124,7 +3267,7 @@
       </c>
       <c r="D2" s="25" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E2" s="24" t="inlineStr">
@@ -1134,89 +3277,89 @@
       </c>
       <c r="F2" s="24" t="inlineStr">
         <is>
-          <t>TARGET HIT (3R)</t>
+          <t>TRAILED (+1.87R)</t>
         </is>
       </c>
       <c r="G2" s="26" t="n">
-        <v>22610.25</v>
+        <v>22975.1</v>
       </c>
       <c r="H2" s="26" t="n">
-        <v>22575.35</v>
+        <v>22941.5</v>
       </c>
       <c r="I2" s="26" t="n">
-        <v>22686.15</v>
+        <v>23075.9</v>
       </c>
       <c r="J2" s="26" t="n">
-        <v>34.9</v>
+        <v>33.6</v>
       </c>
       <c r="K2" s="26" t="n">
-        <v>22686.15</v>
+        <v>23033.5</v>
       </c>
       <c r="L2" s="24" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="M2" s="25" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Partial + Structure Trail</t>
         </is>
       </c>
       <c r="N2" s="26" t="n">
-        <v>75.90000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="O2" s="27" t="n">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="P2" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 22700 CE</t>
+          <t>NIFTY 23100 CE</t>
         </is>
       </c>
       <c r="Q2" s="24" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="R2" s="26" t="n">
-        <v>151.21</v>
+        <v>89.03</v>
       </c>
       <c r="S2" s="26" t="n">
-        <v>185.32</v>
+        <v>111.19</v>
       </c>
       <c r="T2" s="28" t="n">
-        <v>19657</v>
+        <v>17361</v>
       </c>
       <c r="U2" s="28" t="n">
-        <v>24092</v>
+        <v>21682</v>
       </c>
       <c r="V2" s="29" t="n">
-        <v>4344</v>
+        <v>4236</v>
       </c>
       <c r="W2" s="30" t="n">
-        <v>22.1</v>
+        <v>24.4</v>
       </c>
       <c r="X2" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2" s="24" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z2" s="25" t="inlineStr">
         <is>
-          <t>11:20 trendline breakout: 5m close 22,610.25 above descending line 22,606.71 (slope -3.22) | Anchored by swing highs at 09:50 (22,661.45) and 11:05 (22,613.15)</t>
+          <t>12:35 trendline breakout: 5m close 22,975.10 above descending line 22,967.34 (slope -1.59) | Anchored by swing highs at 11:55 (22,978.45) and 12:15 (22,972.10) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="31" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" s="31" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C3" s="32" t="inlineStr">
@@ -1226,7 +3369,7 @@
       </c>
       <c r="D3" s="32" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E3" s="31" t="inlineStr">
@@ -1236,89 +3379,89 @@
       </c>
       <c r="F3" s="31" t="inlineStr">
         <is>
-          <t>TRAILED (+1.05R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G3" s="33" t="n">
-        <v>22736.1</v>
+        <v>23096.8</v>
       </c>
       <c r="H3" s="33" t="n">
-        <v>22790.35</v>
+        <v>23141.15</v>
       </c>
       <c r="I3" s="33" t="n">
-        <v>22491.97</v>
+        <v>22917.3</v>
       </c>
       <c r="J3" s="33" t="n">
-        <v>54.25</v>
+        <v>44.35</v>
       </c>
       <c r="K3" s="33" t="n">
-        <v>22678.95</v>
+        <v>23141.15</v>
       </c>
       <c r="L3" s="31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="M3" s="32" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="N3" s="33" t="n">
-        <v>57.15</v>
-      </c>
-      <c r="O3" s="34" t="n">
-        <v>1.05</v>
+        <v>-44.35</v>
+      </c>
+      <c r="O3" s="42" t="n">
+        <v>-1</v>
       </c>
       <c r="P3" s="32" t="inlineStr">
         <is>
-          <t>NIFTY 22650 PE</t>
+          <t>NIFTY 23000 PE</t>
         </is>
       </c>
       <c r="Q3" s="31" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="R3" s="33" t="n">
-        <v>176.29</v>
+        <v>76.78</v>
       </c>
       <c r="S3" s="33" t="n">
-        <v>201.28</v>
+        <v>61.28</v>
       </c>
       <c r="T3" s="35" t="n">
-        <v>45835</v>
+        <v>14972</v>
       </c>
       <c r="U3" s="35" t="n">
-        <v>52333</v>
-      </c>
-      <c r="V3" s="36" t="n">
-        <v>6356</v>
-      </c>
-      <c r="W3" s="37" t="n">
-        <v>13.9</v>
+        <v>11950</v>
+      </c>
+      <c r="V3" s="43" t="n">
+        <v>-3093</v>
+      </c>
+      <c r="W3" s="44" t="n">
+        <v>-20.7</v>
       </c>
       <c r="X3" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y3" s="31" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z3" s="32" t="inlineStr">
         <is>
-          <t>13:10 trendline breakdown: 5m close 22,736.10 below ascending line 22,756.20 (slope +1.77) | Anchored by swing lows at 11:20 (22,719.10) and 12:20 (22,740.30)</t>
+          <t>13:00 trendline breakdown: 5m close 23,096.80 below ascending line 23,118.65 (slope +2.00) | Anchored by swing lows at 12:05 (23,098.65) and 12:20 (23,104.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C4" s="25" t="inlineStr">
@@ -1328,12 +3471,12 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
@@ -1342,23 +3485,23 @@
         </is>
       </c>
       <c r="G4" s="26" t="n">
-        <v>22781.5</v>
+        <v>22573.4</v>
       </c>
       <c r="H4" s="26" t="n">
-        <v>22744.75</v>
+        <v>22617.45</v>
       </c>
       <c r="I4" s="26" t="n">
-        <v>22891.75</v>
+        <v>22390.45</v>
       </c>
       <c r="J4" s="26" t="n">
-        <v>36.75</v>
+        <v>44.05</v>
       </c>
       <c r="K4" s="26" t="n">
-        <v>22781.5</v>
+        <v>22573.4</v>
       </c>
       <c r="L4" s="24" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="M4" s="25" t="inlineStr">
@@ -1369,58 +3512,58 @@
       <c r="N4" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O4" s="38" t="n">
-        <v>0</v>
+      <c r="O4" s="41" t="n">
+        <v>-0</v>
       </c>
       <c r="P4" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 22900 CE</t>
+          <t>NIFTY 22450 PE</t>
         </is>
       </c>
       <c r="Q4" s="24" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="R4" s="26" t="n">
-        <v>164.2</v>
+        <v>37.68</v>
       </c>
       <c r="S4" s="26" t="n">
-        <v>164.05</v>
+        <v>37.25</v>
       </c>
       <c r="T4" s="28" t="n">
-        <v>42692</v>
+        <v>7348</v>
       </c>
       <c r="U4" s="28" t="n">
-        <v>42653</v>
+        <v>7264</v>
       </c>
       <c r="V4" s="39" t="n">
-        <v>-166</v>
+        <v>-145</v>
       </c>
       <c r="W4" s="40" t="n">
-        <v>-0.4</v>
+        <v>-2</v>
       </c>
       <c r="X4" s="24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y4" s="24" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z4" s="25" t="inlineStr">
         <is>
-          <t>12:40 trendline breakout: 5m close 22,781.50 above descending line 22,776.32 (slope -0.90) | Anchored by swing highs at 10:00 (22,804.35) and 12:00 (22,782.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>11:30 trendline breakdown: 5m close 22,573.40 below ascending line 22,576.72 (slope +7.78) | Anchored by swing lows at 09:40 (22,413.25) and 11:15 (22,561.15) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="31" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -1430,12 +3573,12 @@
       </c>
       <c r="D5" s="32" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E5" s="31" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F5" s="31" t="inlineStr">
@@ -1444,23 +3587,23 @@
         </is>
       </c>
       <c r="G5" s="33" t="n">
-        <v>22573.4</v>
+        <v>22781.5</v>
       </c>
       <c r="H5" s="33" t="n">
-        <v>22617.45</v>
+        <v>22744.75</v>
       </c>
       <c r="I5" s="33" t="n">
-        <v>22390.45</v>
+        <v>22891.75</v>
       </c>
       <c r="J5" s="33" t="n">
-        <v>44.05</v>
+        <v>36.75</v>
       </c>
       <c r="K5" s="33" t="n">
-        <v>22573.4</v>
+        <v>22781.5</v>
       </c>
       <c r="L5" s="31" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="M5" s="32" t="inlineStr">
@@ -1471,98 +3614,98 @@
       <c r="N5" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="41" t="n">
-        <v>-0</v>
+      <c r="O5" s="45" t="n">
+        <v>0</v>
       </c>
       <c r="P5" s="32" t="inlineStr">
         <is>
-          <t>NIFTY 22450 PE</t>
+          <t>NIFTY 22900 CE</t>
         </is>
       </c>
       <c r="Q5" s="31" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="R5" s="33" t="n">
-        <v>37.68</v>
+        <v>164.2</v>
       </c>
       <c r="S5" s="33" t="n">
-        <v>37.25</v>
+        <v>164.05</v>
       </c>
       <c r="T5" s="35" t="n">
-        <v>7348</v>
+        <v>42692</v>
       </c>
       <c r="U5" s="35" t="n">
-        <v>7264</v>
-      </c>
-      <c r="V5" s="42" t="n">
-        <v>-145</v>
-      </c>
-      <c r="W5" s="43" t="n">
-        <v>-2</v>
+        <v>42653</v>
+      </c>
+      <c r="V5" s="43" t="n">
+        <v>-166</v>
+      </c>
+      <c r="W5" s="44" t="n">
+        <v>-0.4</v>
       </c>
       <c r="X5" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y5" s="31" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="Z5" s="32" t="inlineStr">
         <is>
-          <t>11:30 trendline breakdown: 5m close 22,573.40 below ascending line 22,576.72 (slope +7.78) | Anchored by swing lows at 09:40 (22,413.25) and 11:15 (22,561.15) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>12:40 trendline breakout: 5m close 22,781.50 above descending line 22,776.32 (slope -0.90) | Anchored by swing highs at 10:00 (22,804.35) and 12:00 (22,782.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Trendline Reversal</t>
         </is>
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
+          <t>Trendline Breakdown [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>TRAILED (+0.89R)</t>
+          <t>TRAILED (+1.05R)</t>
         </is>
       </c>
       <c r="G6" s="26" t="n">
-        <v>22712.95</v>
+        <v>22736.1</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>22671.3</v>
+        <v>22790.35</v>
       </c>
       <c r="I6" s="26" t="n">
-        <v>22900.38</v>
+        <v>22491.97</v>
       </c>
       <c r="J6" s="26" t="n">
-        <v>41.65</v>
+        <v>54.25</v>
       </c>
       <c r="K6" s="26" t="n">
-        <v>22749.9</v>
+        <v>22678.95</v>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="M6" s="25" t="inlineStr">
@@ -1571,172 +3714,172 @@
         </is>
       </c>
       <c r="N6" s="26" t="n">
-        <v>36.95</v>
+        <v>57.15</v>
       </c>
       <c r="O6" s="27" t="n">
-        <v>0.89</v>
+        <v>1.05</v>
       </c>
       <c r="P6" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 22800 CE</t>
+          <t>NIFTY 22650 PE</t>
         </is>
       </c>
       <c r="Q6" s="24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="R6" s="26" t="n">
-        <v>129.77</v>
+        <v>176.29</v>
       </c>
       <c r="S6" s="26" t="n">
-        <v>145.68</v>
+        <v>201.28</v>
       </c>
       <c r="T6" s="28" t="n">
-        <v>16870</v>
+        <v>45835</v>
       </c>
       <c r="U6" s="28" t="n">
-        <v>18938</v>
+        <v>52333</v>
       </c>
       <c r="V6" s="29" t="n">
-        <v>1987</v>
+        <v>6356</v>
       </c>
       <c r="W6" s="30" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="X6" s="24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y6" s="24" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z6" s="25" t="inlineStr">
         <is>
-          <t>10:25 breakout: 5m high 22,742.50 cleared OR-30H 22,690.45 | 10:50 retest: 5m low 22,676.30 tested OR-30H 22,690.45 as support | 10:55 confirmation: 5m close 22,712.95 held above OR-30H and VWAP</t>
+          <t>13:10 trendline breakdown: 5m close 22,736.10 below ascending line 22,756.20 (slope +1.77) | Anchored by swing lows at 11:20 (22,719.10) and 12:20 (22,740.30)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" s="31" t="inlineStr">
         <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>Trendline Reversal</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>Trendline Breakout [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>TRAILED (+0.16R)</t>
+        </is>
+      </c>
+      <c r="G7" s="33" t="n">
+        <v>22610.25</v>
+      </c>
+      <c r="H7" s="33" t="n">
+        <v>22575.35</v>
+      </c>
+      <c r="I7" s="33" t="n">
+        <v>22686.15</v>
+      </c>
+      <c r="J7" s="33" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="K7" s="33" t="n">
+        <v>22615.85</v>
+      </c>
+      <c r="L7" s="31" t="inlineStr">
+        <is>
           <t>11:55</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
-        <is>
-          <t>Breakout &amp; Retest (PD)</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="inlineStr">
-        <is>
-          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="F7" s="31" t="inlineStr">
-        <is>
-          <t>TARGET HIT (3R)</t>
-        </is>
-      </c>
-      <c r="G7" s="33" t="n">
-        <v>22818.45</v>
-      </c>
-      <c r="H7" s="33" t="n">
-        <v>22850.55</v>
-      </c>
-      <c r="I7" s="33" t="n">
-        <v>22722.15</v>
-      </c>
-      <c r="J7" s="33" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="K7" s="33" t="n">
-        <v>22722.15</v>
-      </c>
-      <c r="L7" s="31" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="M7" s="32" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N7" s="33" t="n">
-        <v>96.3</v>
+        <v>5.6</v>
       </c>
       <c r="O7" s="34" t="n">
-        <v>2.5</v>
+        <v>0.16</v>
       </c>
       <c r="P7" s="32" t="inlineStr">
         <is>
-          <t>NIFTY 22700 PE</t>
+          <t>NIFTY 22700 CE</t>
         </is>
       </c>
       <c r="Q7" s="31" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="R7" s="33" t="n">
-        <v>121.21</v>
+        <v>151.21</v>
       </c>
       <c r="S7" s="33" t="n">
-        <v>162.55</v>
+        <v>153.26</v>
       </c>
       <c r="T7" s="35" t="n">
-        <v>15757</v>
+        <v>29486</v>
       </c>
       <c r="U7" s="35" t="n">
-        <v>21132</v>
+        <v>29886</v>
       </c>
       <c r="V7" s="36" t="n">
-        <v>5290</v>
+        <v>297</v>
       </c>
       <c r="W7" s="37" t="n">
-        <v>33.6</v>
+        <v>1</v>
       </c>
       <c r="X7" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y7" s="31" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z7" s="32" t="inlineStr">
         <is>
-          <t>11:40 breakdown: 5m low 22,839.70 breached PDL 22,845.25 | 11:45 retest: 5m high 22,841.90 tested PDL 22,845.25 as resistance | 11:55 confirmation: 5m close 22,818.45 held below PDL and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+          <t>11:20 trendline breakout: 5m close 22,610.25 above descending line 22,606.71 (slope -3.22) | Anchored by swing highs at 09:50 (22,661.45) and 11:05 (22,613.15)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="C8" s="25" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Trendline Reversal</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>Micro Trendline Breakdown [1M Micro-Execution]</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -1746,822 +3889,108 @@
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+1.00R)</t>
         </is>
       </c>
       <c r="G8" s="26" t="n">
-        <v>22936.05</v>
+        <v>22852.55</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>22979.15</v>
+        <v>22873</v>
       </c>
       <c r="I8" s="26" t="n">
-        <v>22848.25</v>
+        <v>22780.85</v>
       </c>
       <c r="J8" s="26" t="n">
-        <v>43.1</v>
+        <v>20.45</v>
       </c>
       <c r="K8" s="26" t="n">
-        <v>22979.15</v>
+        <v>22828</v>
       </c>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="M8" s="25" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Trailed Stop Hit (+1.0R Locked)</t>
         </is>
       </c>
       <c r="N8" s="26" t="n">
-        <v>-43.1</v>
-      </c>
-      <c r="O8" s="44" t="n">
-        <v>-1</v>
+        <v>7.65</v>
+      </c>
+      <c r="O8" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="P8" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 22850 PE</t>
+          <t>NIFTY 22750 PE</t>
         </is>
       </c>
       <c r="Q8" s="24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="R8" s="26" t="n">
-        <v>136.34</v>
+        <v>102.37</v>
       </c>
       <c r="S8" s="26" t="n">
-        <v>118.95</v>
+        <v>110.02</v>
       </c>
       <c r="T8" s="28" t="n">
-        <v>17724</v>
+        <v>26616</v>
       </c>
       <c r="U8" s="28" t="n">
-        <v>15464</v>
-      </c>
-      <c r="V8" s="39" t="n">
-        <v>-2338</v>
-      </c>
-      <c r="W8" s="40" t="n">
-        <v>-13.2</v>
+        <v>28605</v>
+      </c>
+      <c r="V8" s="29" t="n">
+        <v>1989</v>
+      </c>
+      <c r="W8" s="30" t="n">
+        <v>7.5</v>
       </c>
       <c r="X8" s="24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y8" s="24" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z8" s="25" t="inlineStr">
         <is>
-          <t>10:10 breakdown: 5m low 22,950.90 breached OR-30L 22,981.35 | 10:15 retest: 5m high 22,974.15 tested OR-30L 22,981.35 as resistance | 10:20 confirmation: 5m close 22,936.05 held below OR-30L and VWAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="C9" s="32" t="inlineStr">
-        <is>
-          <t>Breakout &amp; Retest (PD)</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>PDL Resistance Flip [Tier 1 (General]</t>
-        </is>
-      </c>
-      <c r="E9" s="31" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="F9" s="31" t="inlineStr">
-        <is>
-          <t>FLAT</t>
-        </is>
-      </c>
-      <c r="G9" s="33" t="n">
-        <v>22891.95</v>
-      </c>
-      <c r="H9" s="33" t="n">
-        <v>22932.2</v>
-      </c>
-      <c r="I9" s="33" t="n">
-        <v>22771.2</v>
-      </c>
-      <c r="J9" s="33" t="n">
-        <v>40.25</v>
-      </c>
-      <c r="K9" s="33" t="n">
-        <v>22891.95</v>
-      </c>
-      <c r="L9" s="31" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="M9" s="32" t="inlineStr">
-        <is>
-          <t>Breakeven</t>
-        </is>
-      </c>
-      <c r="N9" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="41" t="n">
-        <v>-0</v>
-      </c>
-      <c r="P9" s="32" t="inlineStr">
-        <is>
-          <t>NIFTY 22850 PE</t>
-        </is>
-      </c>
-      <c r="Q9" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="R9" s="33" t="n">
-        <v>170.75</v>
-      </c>
-      <c r="S9" s="33" t="n">
-        <v>170.38</v>
-      </c>
-      <c r="T9" s="35" t="n">
-        <v>33296</v>
-      </c>
-      <c r="U9" s="35" t="n">
-        <v>33224</v>
-      </c>
-      <c r="V9" s="42" t="n">
-        <v>-181</v>
-      </c>
-      <c r="W9" s="43" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="X9" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y9" s="31" t="n">
-        <v>195</v>
-      </c>
-      <c r="Z9" s="32" t="inlineStr">
-        <is>
-          <t>13:00 breakdown: 5m low 22,906.00 breached PDL 22,914.30 | 13:15 retest: 5m high 22,927.20 tested PDL 22,914.30 as resistance | 13:20 confirmation: 5m close 22,891.95 held below PDL and VWAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="C10" s="25" t="inlineStr">
-        <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
-        </is>
-      </c>
-      <c r="D10" s="25" t="inlineStr">
-        <is>
-          <t>OR-30L Resistance Flip [Tier 1 (General]</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>FLAT</t>
-        </is>
-      </c>
-      <c r="G10" s="26" t="n">
-        <v>22945.55</v>
-      </c>
-      <c r="H10" s="26" t="n">
-        <v>22983.55</v>
-      </c>
-      <c r="I10" s="26" t="n">
-        <v>22831.55</v>
-      </c>
-      <c r="J10" s="26" t="n">
-        <v>38</v>
-      </c>
-      <c r="K10" s="26" t="n">
-        <v>22945.55</v>
-      </c>
-      <c r="L10" s="24" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="M10" s="25" t="inlineStr">
-        <is>
-          <t>Breakeven</t>
-        </is>
-      </c>
-      <c r="N10" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="38" t="n">
-        <v>-0</v>
-      </c>
-      <c r="P10" s="25" t="inlineStr">
-        <is>
-          <t>NIFTY 22900 PE</t>
-        </is>
-      </c>
-      <c r="Q10" s="24" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="R10" s="26" t="n">
-        <v>170.04</v>
-      </c>
-      <c r="S10" s="26" t="n">
-        <v>169.63</v>
-      </c>
-      <c r="T10" s="28" t="n">
-        <v>33158</v>
-      </c>
-      <c r="U10" s="28" t="n">
-        <v>33078</v>
-      </c>
-      <c r="V10" s="39" t="n">
-        <v>-189</v>
-      </c>
-      <c r="W10" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="X10" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y10" s="24" t="n">
-        <v>195</v>
-      </c>
-      <c r="Z10" s="25" t="inlineStr">
-        <is>
-          <t>12:05 breakdown: 5m low 22,948.75 breached OR-30L 22,970.85 | 12:10 retest: 5m high 22,978.55 tested OR-30L 22,970.85 as resistance | 12:15 confirmation: 5m close 22,945.55 held below OR-30L and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C11" s="32" t="inlineStr">
-        <is>
-          <t>Trendline Reversal</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="inlineStr">
-        <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
-        </is>
-      </c>
-      <c r="E11" s="31" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="F11" s="31" t="inlineStr">
-        <is>
-          <t>STOPPED OUT (-1R)</t>
-        </is>
-      </c>
-      <c r="G11" s="33" t="n">
-        <v>23096.8</v>
-      </c>
-      <c r="H11" s="33" t="n">
-        <v>23141.15</v>
-      </c>
-      <c r="I11" s="33" t="n">
-        <v>22917.3</v>
-      </c>
-      <c r="J11" s="33" t="n">
-        <v>44.35</v>
-      </c>
-      <c r="K11" s="33" t="n">
-        <v>23141.15</v>
-      </c>
-      <c r="L11" s="31" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="M11" s="32" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="N11" s="33" t="n">
-        <v>-44.35</v>
-      </c>
-      <c r="O11" s="45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P11" s="32" t="inlineStr">
-        <is>
-          <t>NIFTY 23000 PE</t>
-        </is>
-      </c>
-      <c r="Q11" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="R11" s="33" t="n">
-        <v>76.78</v>
-      </c>
-      <c r="S11" s="33" t="n">
-        <v>61.28</v>
-      </c>
-      <c r="T11" s="35" t="n">
-        <v>9981</v>
-      </c>
-      <c r="U11" s="35" t="n">
-        <v>7966</v>
-      </c>
-      <c r="V11" s="42" t="n">
-        <v>-2078</v>
-      </c>
-      <c r="W11" s="43" t="n">
-        <v>-20.8</v>
-      </c>
-      <c r="X11" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y11" s="31" t="n">
-        <v>130</v>
-      </c>
-      <c r="Z11" s="32" t="inlineStr">
-        <is>
-          <t>13:00 trendline breakdown: 5m close 23,096.80 below ascending line 23,118.65 (slope +2.00) | Anchored by swing lows at 12:05 (23,098.65) and 12:20 (23,104.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="C12" s="25" t="inlineStr">
-        <is>
-          <t>Breakout &amp; Retest (PD)</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="inlineStr">
-        <is>
-          <t>PDH Support Flip [Tier 2 (Super-Trend]</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="F12" s="24" t="inlineStr">
-        <is>
-          <t>TRAILED (+0.99R)</t>
-        </is>
-      </c>
-      <c r="G12" s="26" t="n">
-        <v>23088.9</v>
-      </c>
-      <c r="H12" s="26" t="n">
-        <v>23054.45</v>
-      </c>
-      <c r="I12" s="26" t="n">
-        <v>23192.25</v>
-      </c>
-      <c r="J12" s="26" t="n">
-        <v>34.45</v>
-      </c>
-      <c r="K12" s="26" t="n">
-        <v>23123.05</v>
-      </c>
-      <c r="L12" s="24" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="M12" s="25" t="inlineStr">
-        <is>
-          <t>Structure Trail</t>
-        </is>
-      </c>
-      <c r="N12" s="26" t="n">
-        <v>34.15</v>
-      </c>
-      <c r="O12" s="27" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="P12" s="25" t="inlineStr">
-        <is>
-          <t>NIFTY 23200 CE</t>
-        </is>
-      </c>
-      <c r="Q12" s="24" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="R12" s="26" t="n">
-        <v>73.34999999999999</v>
-      </c>
-      <c r="S12" s="26" t="n">
-        <v>85.19</v>
-      </c>
-      <c r="T12" s="28" t="n">
-        <v>9536</v>
-      </c>
-      <c r="U12" s="28" t="n">
-        <v>11075</v>
-      </c>
-      <c r="V12" s="29" t="n">
-        <v>1472</v>
-      </c>
-      <c r="W12" s="30" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="X12" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y12" s="24" t="n">
-        <v>130</v>
-      </c>
-      <c r="Z12" s="25" t="inlineStr">
-        <is>
-          <t>10:15 breakout: 5m high 23,094.60 cleared PDH 23,056.20 | 11:10 retest: 5m low 23,066.70 tested PDH 23,056.20 as support | 11:15 confirmation: 5m close 23,088.90 held above PDH and VWAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B13" s="31" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="C13" s="32" t="inlineStr">
-        <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
-        </is>
-      </c>
-      <c r="D13" s="32" t="inlineStr">
-        <is>
-          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
-        </is>
-      </c>
-      <c r="E13" s="31" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="F13" s="31" t="inlineStr">
-        <is>
-          <t>STOPPED OUT (-1R)</t>
-        </is>
-      </c>
-      <c r="G13" s="33" t="n">
-        <v>23109.55</v>
-      </c>
-      <c r="H13" s="33" t="n">
-        <v>23072.2</v>
-      </c>
-      <c r="I13" s="33" t="n">
-        <v>23221.6</v>
-      </c>
-      <c r="J13" s="33" t="n">
-        <v>37.35</v>
-      </c>
-      <c r="K13" s="33" t="n">
-        <v>23072.2</v>
-      </c>
-      <c r="L13" s="31" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="M13" s="32" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="N13" s="33" t="n">
-        <v>-37.35</v>
-      </c>
-      <c r="O13" s="45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P13" s="32" t="inlineStr">
-        <is>
-          <t>NIFTY 23200 CE</t>
-        </is>
-      </c>
-      <c r="Q13" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="R13" s="33" t="n">
-        <v>81.22</v>
-      </c>
-      <c r="S13" s="33" t="n">
-        <v>67.58</v>
-      </c>
-      <c r="T13" s="35" t="n">
-        <v>10559</v>
-      </c>
-      <c r="U13" s="35" t="n">
-        <v>8785</v>
-      </c>
-      <c r="V13" s="42" t="n">
-        <v>-1838</v>
-      </c>
-      <c r="W13" s="43" t="n">
-        <v>-17.4</v>
-      </c>
-      <c r="X13" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y13" s="31" t="n">
-        <v>130</v>
-      </c>
-      <c r="Z13" s="32" t="inlineStr">
-        <is>
-          <t>10:15 breakout: 5m high 23,094.60 cleared OR-30H 23,076.10 | 10:50 retest: 5m low 23,082.25 tested OR-30H 23,076.10 as support | 11:00 confirmation: 5m close 23,109.55 held above OR-30H and VWAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="C14" s="25" t="inlineStr">
-        <is>
-          <t>Trendline Reversal</t>
-        </is>
-      </c>
-      <c r="D14" s="25" t="inlineStr">
-        <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="F14" s="24" t="inlineStr">
-        <is>
-          <t>TRAILED (+1.87R)</t>
-        </is>
-      </c>
-      <c r="G14" s="26" t="n">
-        <v>22975.1</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>22941.5</v>
-      </c>
-      <c r="I14" s="26" t="n">
-        <v>23075.9</v>
-      </c>
-      <c r="J14" s="26" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="K14" s="26" t="n">
-        <v>23033.5</v>
-      </c>
-      <c r="L14" s="24" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="M14" s="25" t="inlineStr">
-        <is>
-          <t>Partial + Structure Trail</t>
-        </is>
-      </c>
-      <c r="N14" s="26" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="O14" s="27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="P14" s="25" t="inlineStr">
-        <is>
-          <t>NIFTY 23100 CE</t>
-        </is>
-      </c>
-      <c r="Q14" s="24" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="R14" s="26" t="n">
-        <v>89.03</v>
-      </c>
-      <c r="S14" s="26" t="n">
-        <v>111.19</v>
-      </c>
-      <c r="T14" s="28" t="n">
-        <v>11574</v>
-      </c>
-      <c r="U14" s="28" t="n">
-        <v>14455</v>
-      </c>
-      <c r="V14" s="29" t="n">
-        <v>2808</v>
-      </c>
-      <c r="W14" s="30" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X14" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y14" s="24" t="n">
-        <v>130</v>
-      </c>
-      <c r="Z14" s="25" t="inlineStr">
-        <is>
-          <t>12:35 trendline breakout: 5m close 22,975.10 above descending line 22,967.34 (slope -1.59) | Anchored by swing highs at 11:55 (22,978.45) and 12:15 (22,972.10) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B15" s="31" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="C15" s="32" t="inlineStr">
-        <is>
-          <t>Breakout &amp; Retest (PD)</t>
-        </is>
-      </c>
-      <c r="D15" s="32" t="inlineStr">
-        <is>
-          <t>PDH Support Flip [Tier 2 (Super-Trend]</t>
-        </is>
-      </c>
-      <c r="E15" s="31" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="F15" s="31" t="inlineStr">
-        <is>
-          <t>TARGET HIT (3R)</t>
-        </is>
-      </c>
-      <c r="G15" s="33" t="n">
-        <v>22787.2</v>
-      </c>
-      <c r="H15" s="33" t="n">
-        <v>22739.35</v>
-      </c>
-      <c r="I15" s="33" t="n">
-        <v>22930.75</v>
-      </c>
-      <c r="J15" s="33" t="n">
-        <v>47.85</v>
-      </c>
-      <c r="K15" s="33" t="n">
-        <v>22930.75</v>
-      </c>
-      <c r="L15" s="31" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="M15" s="32" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="N15" s="33" t="n">
-        <v>143.55</v>
-      </c>
-      <c r="O15" s="34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P15" s="32" t="inlineStr">
-        <is>
-          <t>NIFTY 22900 CE</t>
-        </is>
-      </c>
-      <c r="Q15" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="R15" s="33" t="n">
-        <v>94.22</v>
-      </c>
-      <c r="S15" s="33" t="n">
-        <v>159.33</v>
-      </c>
-      <c r="T15" s="35" t="n">
-        <v>12249</v>
-      </c>
-      <c r="U15" s="35" t="n">
-        <v>20713</v>
-      </c>
-      <c r="V15" s="36" t="n">
-        <v>8382</v>
-      </c>
-      <c r="W15" s="37" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="X15" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y15" s="31" t="n">
-        <v>130</v>
-      </c>
-      <c r="Z15" s="32" t="inlineStr">
-        <is>
-          <t>09:35 breakout: 5m high 22,771.55 cleared PDH 22,757.80 | 09:40 retest: 5m low 22,748.55 tested PDH 22,757.80 as support | 09:50 confirmation: 5m close 22,787.20 held above PDH and VWAP</t>
+          <t>10:36 1M CHoCH breakdown of ascending trendline below VWAP. Trailed stop hit at 11:14 IST after +2R milestone reached.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z15"/>
+  <autoFilter ref="A1:Z8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
@@ -2575,6 +4004,7 @@
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="65" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2708,26 +4138,27 @@
           <t>Rationale</t>
         </is>
       </c>
+      <c r="AA1" s="23" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" s="24" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="C2" s="25" t="inlineStr">
         <is>
-          <t>Trendline Reversal</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D2" s="25" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>PDH Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E2" s="24" t="inlineStr">
@@ -2741,23 +4172,23 @@
         </is>
       </c>
       <c r="G2" s="26" t="n">
-        <v>22610.25</v>
+        <v>22787.2</v>
       </c>
       <c r="H2" s="26" t="n">
-        <v>22575.35</v>
+        <v>22739.35</v>
       </c>
       <c r="I2" s="26" t="n">
-        <v>22686.15</v>
+        <v>22930.75</v>
       </c>
       <c r="J2" s="26" t="n">
-        <v>34.9</v>
+        <v>47.85</v>
       </c>
       <c r="K2" s="26" t="n">
-        <v>22686.15</v>
+        <v>22930.75</v>
       </c>
       <c r="L2" s="24" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="M2" s="25" t="inlineStr">
@@ -2766,172 +4197,174 @@
         </is>
       </c>
       <c r="N2" s="26" t="n">
-        <v>75.90000000000001</v>
+        <v>143.55</v>
       </c>
       <c r="O2" s="27" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="P2" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 22700 CE</t>
+          <t>NIFTY 22900 CE</t>
         </is>
       </c>
       <c r="Q2" s="24" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="R2" s="26" t="n">
-        <v>151.21</v>
+        <v>94.22</v>
       </c>
       <c r="S2" s="26" t="n">
-        <v>185.32</v>
+        <v>159.33</v>
       </c>
       <c r="T2" s="28" t="n">
-        <v>19657</v>
+        <v>18373</v>
       </c>
       <c r="U2" s="28" t="n">
-        <v>24092</v>
+        <v>31069</v>
       </c>
       <c r="V2" s="29" t="n">
-        <v>4344</v>
+        <v>12597</v>
       </c>
       <c r="W2" s="30" t="n">
-        <v>22.1</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="X2" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2" s="24" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z2" s="25" t="inlineStr">
         <is>
-          <t>11:20 trendline breakout: 5m close 22,610.25 above descending line 22,606.71 (slope -3.22) | Anchored by swing highs at 09:50 (22,661.45) and 11:05 (22,613.15)</t>
-        </is>
-      </c>
+          <t>09:35 breakout: 5m high 22,771.55 cleared PDH 22,757.80 | 09:40 retest: 5m low 22,748.55 tested PDH 22,757.80 as support | 09:50 confirmation: 5m close 22,787.20 held above PDH and VWAP</t>
+        </is>
+      </c>
+      <c r="AA2" s="25" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="31" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" s="31" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" s="32" t="inlineStr">
         <is>
-          <t>Trendline Reversal</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D3" s="32" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>OR-30H Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E3" s="31" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F3" s="31" t="inlineStr">
         <is>
-          <t>TRAILED (+1.05R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G3" s="33" t="n">
-        <v>22736.1</v>
+        <v>23109.55</v>
       </c>
       <c r="H3" s="33" t="n">
-        <v>22790.35</v>
+        <v>23072.2</v>
       </c>
       <c r="I3" s="33" t="n">
-        <v>22491.97</v>
+        <v>23221.6</v>
       </c>
       <c r="J3" s="33" t="n">
-        <v>54.25</v>
+        <v>37.35</v>
       </c>
       <c r="K3" s="33" t="n">
-        <v>22678.95</v>
+        <v>23072.2</v>
       </c>
       <c r="L3" s="31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="M3" s="32" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="N3" s="33" t="n">
-        <v>57.15</v>
-      </c>
-      <c r="O3" s="34" t="n">
-        <v>1.05</v>
+        <v>-37.35</v>
+      </c>
+      <c r="O3" s="42" t="n">
+        <v>-1</v>
       </c>
       <c r="P3" s="32" t="inlineStr">
         <is>
-          <t>NIFTY 22650 PE</t>
+          <t>NIFTY 23200 CE</t>
         </is>
       </c>
       <c r="Q3" s="31" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="R3" s="33" t="n">
-        <v>176.29</v>
+        <v>81.22</v>
       </c>
       <c r="S3" s="33" t="n">
-        <v>201.28</v>
+        <v>67.58</v>
       </c>
       <c r="T3" s="35" t="n">
-        <v>45835</v>
+        <v>15838</v>
       </c>
       <c r="U3" s="35" t="n">
-        <v>52333</v>
-      </c>
-      <c r="V3" s="36" t="n">
-        <v>6356</v>
-      </c>
-      <c r="W3" s="37" t="n">
-        <v>13.9</v>
+        <v>13178</v>
+      </c>
+      <c r="V3" s="43" t="n">
+        <v>-2733</v>
+      </c>
+      <c r="W3" s="44" t="n">
+        <v>-17.3</v>
       </c>
       <c r="X3" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y3" s="31" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z3" s="32" t="inlineStr">
         <is>
-          <t>13:10 trendline breakdown: 5m close 22,736.10 below ascending line 22,756.20 (slope +1.77) | Anchored by swing lows at 11:20 (22,719.10) and 12:20 (22,740.30)</t>
-        </is>
-      </c>
+          <t>10:15 breakout: 5m high 23,094.60 cleared OR-30H 23,076.10 | 10:50 retest: 5m low 23,082.25 tested OR-30H 23,076.10 as support | 11:00 confirmation: 5m close 23,109.55 held above OR-30H and VWAP</t>
+        </is>
+      </c>
+      <c r="AA3" s="32" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t>Trendline Reversal</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>PDH Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
@@ -2941,99 +4374,100 @@
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>TRAILED (+0.99R)</t>
         </is>
       </c>
       <c r="G4" s="26" t="n">
-        <v>22781.5</v>
+        <v>23088.9</v>
       </c>
       <c r="H4" s="26" t="n">
-        <v>22744.75</v>
+        <v>23054.45</v>
       </c>
       <c r="I4" s="26" t="n">
-        <v>22891.75</v>
+        <v>23192.25</v>
       </c>
       <c r="J4" s="26" t="n">
-        <v>36.75</v>
+        <v>34.45</v>
       </c>
       <c r="K4" s="26" t="n">
-        <v>22781.5</v>
+        <v>23123.05</v>
       </c>
       <c r="L4" s="24" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="M4" s="25" t="inlineStr">
         <is>
-          <t>Breakeven</t>
+          <t>Structure Trail</t>
         </is>
       </c>
       <c r="N4" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="38" t="n">
-        <v>0</v>
+        <v>34.15</v>
+      </c>
+      <c r="O4" s="27" t="n">
+        <v>0.99</v>
       </c>
       <c r="P4" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 22900 CE</t>
+          <t>NIFTY 23200 CE</t>
         </is>
       </c>
       <c r="Q4" s="24" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="R4" s="26" t="n">
-        <v>164.2</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="S4" s="26" t="n">
-        <v>164.05</v>
+        <v>85.19</v>
       </c>
       <c r="T4" s="28" t="n">
-        <v>42692</v>
+        <v>14303</v>
       </c>
       <c r="U4" s="28" t="n">
-        <v>42653</v>
-      </c>
-      <c r="V4" s="39" t="n">
-        <v>-166</v>
-      </c>
-      <c r="W4" s="40" t="n">
-        <v>-0.4</v>
+        <v>16612</v>
+      </c>
+      <c r="V4" s="29" t="n">
+        <v>2232</v>
+      </c>
+      <c r="W4" s="30" t="n">
+        <v>15.6</v>
       </c>
       <c r="X4" s="24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y4" s="24" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z4" s="25" t="inlineStr">
         <is>
-          <t>12:40 trendline breakout: 5m close 22,781.50 above descending line 22,776.32 (slope -0.90) | Anchored by swing highs at 10:00 (22,804.35) and 12:00 (22,782.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
-        </is>
-      </c>
+          <t>10:15 breakout: 5m high 23,094.60 cleared PDH 23,056.20 | 11:10 retest: 5m low 23,066.70 tested PDH 23,056.20 as support | 11:15 confirmation: 5m close 23,088.90 held above PDH and VWAP</t>
+        </is>
+      </c>
+      <c r="AA4" s="25" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="31" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
         <is>
-          <t>Trendline Reversal</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D5" s="32" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 3 Lots (195 Qty)]</t>
         </is>
       </c>
       <c r="E5" s="31" t="inlineStr">
@@ -3043,43 +4477,43 @@
       </c>
       <c r="F5" s="31" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>TRAILED (+0.38R)</t>
         </is>
       </c>
       <c r="G5" s="33" t="n">
-        <v>22573.4</v>
+        <v>22945.55</v>
       </c>
       <c r="H5" s="33" t="n">
-        <v>22617.45</v>
+        <v>22983.55</v>
       </c>
       <c r="I5" s="33" t="n">
-        <v>22390.45</v>
+        <v>22831.55</v>
       </c>
       <c r="J5" s="33" t="n">
-        <v>44.05</v>
+        <v>38</v>
       </c>
       <c r="K5" s="33" t="n">
-        <v>22573.4</v>
+        <v>22931.3</v>
       </c>
       <c r="L5" s="31" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="M5" s="32" t="inlineStr">
         <is>
-          <t>Breakeven</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N5" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="41" t="n">
-        <v>-0</v>
+        <v>14.25</v>
+      </c>
+      <c r="O5" s="34" t="n">
+        <v>0.38</v>
       </c>
       <c r="P5" s="32" t="inlineStr">
         <is>
-          <t>NIFTY 22450 PE</t>
+          <t>NIFTY 22850 PE</t>
         </is>
       </c>
       <c r="Q5" s="31" t="inlineStr">
@@ -3088,22 +4522,22 @@
         </is>
       </c>
       <c r="R5" s="33" t="n">
-        <v>37.68</v>
+        <v>147.75</v>
       </c>
       <c r="S5" s="33" t="n">
-        <v>37.25</v>
+        <v>153.49</v>
       </c>
       <c r="T5" s="35" t="n">
-        <v>7348</v>
+        <v>28811</v>
       </c>
       <c r="U5" s="35" t="n">
-        <v>7264</v>
-      </c>
-      <c r="V5" s="42" t="n">
-        <v>-145</v>
-      </c>
-      <c r="W5" s="43" t="n">
-        <v>-2</v>
+        <v>29931</v>
+      </c>
+      <c r="V5" s="36" t="n">
+        <v>1017</v>
+      </c>
+      <c r="W5" s="37" t="n">
+        <v>3.5</v>
       </c>
       <c r="X5" s="31" t="n">
         <v>3</v>
@@ -3113,29 +4547,30 @@
       </c>
       <c r="Z5" s="32" t="inlineStr">
         <is>
-          <t>11:30 trendline breakdown: 5m close 22,573.40 below ascending line 22,576.72 (slope +7.78) | Anchored by swing lows at 09:40 (22,413.25) and 11:15 (22,561.15) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
-        </is>
-      </c>
+          <t>12:05 breakdown: 5m low 22,948.75 breached OR-30L 22,970.85 | 12:10 retest: 5m high 22,978.55 tested OR-30L 22,970.85 as resistance | 12:15 confirmation: 5m close 22,945.55 held below OR-30L and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+        </is>
+      </c>
+      <c r="AA5" s="32" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>Trendline Reversal</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>Trendline Breakdown [Tier 2 (Super-Trend]</t>
+          <t>PDL Resistance Flip [Preferred Lot Size: 3 Lots (195 Qty)]</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -3145,205 +4580,812 @@
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>FLAT</t>
         </is>
       </c>
       <c r="G6" s="26" t="n">
-        <v>23096.8</v>
+        <v>22891.95</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>23141.15</v>
+        <v>22932.2</v>
       </c>
       <c r="I6" s="26" t="n">
-        <v>22917.3</v>
+        <v>22771.2</v>
       </c>
       <c r="J6" s="26" t="n">
-        <v>44.35</v>
+        <v>40.25</v>
       </c>
       <c r="K6" s="26" t="n">
-        <v>23141.15</v>
+        <v>22891.95</v>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="M6" s="25" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Breakeven</t>
         </is>
       </c>
       <c r="N6" s="26" t="n">
-        <v>-44.35</v>
-      </c>
-      <c r="O6" s="44" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="O6" s="41" t="n">
+        <v>-0</v>
       </c>
       <c r="P6" s="25" t="inlineStr">
         <is>
-          <t>NIFTY 23000 PE</t>
+          <t>NIFTY 22800 PE</t>
         </is>
       </c>
       <c r="Q6" s="24" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="R6" s="26" t="n">
-        <v>76.78</v>
+        <v>148.32</v>
       </c>
       <c r="S6" s="26" t="n">
-        <v>61.28</v>
+        <v>147.96</v>
       </c>
       <c r="T6" s="28" t="n">
-        <v>9981</v>
+        <v>28922</v>
       </c>
       <c r="U6" s="28" t="n">
-        <v>7966</v>
+        <v>28852</v>
       </c>
       <c r="V6" s="39" t="n">
-        <v>-2078</v>
+        <v>-171</v>
       </c>
       <c r="W6" s="40" t="n">
-        <v>-20.8</v>
+        <v>-0.6</v>
       </c>
       <c r="X6" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6" s="24" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z6" s="25" t="inlineStr">
         <is>
-          <t>13:00 trendline breakdown: 5m close 23,096.80 below ascending line 23,118.65 (slope +2.00) | Anchored by swing lows at 12:05 (23,098.65) and 12:20 (23,104.65) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
-        </is>
-      </c>
+          <t>13:00 breakdown: 5m low 22,906.00 breached PDL 22,914.30 | 13:15 retest: 5m high 22,927.20 tested PDL 22,914.30 as resistance | 13:20 confirmation: 5m close 22,891.95 held below PDL and VWAP</t>
+        </is>
+      </c>
+      <c r="AA6" s="25" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" s="31" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>Trendline Reversal</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D7" s="32" t="inlineStr">
         <is>
-          <t>Trendline Breakout [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E7" s="31" t="inlineStr">
         <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>STOPPED OUT (-1R)</t>
+        </is>
+      </c>
+      <c r="G7" s="33" t="n">
+        <v>22936.05</v>
+      </c>
+      <c r="H7" s="33" t="n">
+        <v>22979.15</v>
+      </c>
+      <c r="I7" s="33" t="n">
+        <v>22848.25</v>
+      </c>
+      <c r="J7" s="33" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="K7" s="33" t="n">
+        <v>22979.15</v>
+      </c>
+      <c r="L7" s="31" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="M7" s="32" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="N7" s="33" t="n">
+        <v>-43.1</v>
+      </c>
+      <c r="O7" s="42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P7" s="32" t="inlineStr">
+        <is>
+          <t>NIFTY 22850 PE</t>
+        </is>
+      </c>
+      <c r="Q7" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="R7" s="33" t="n">
+        <v>136.34</v>
+      </c>
+      <c r="S7" s="33" t="n">
+        <v>118.95</v>
+      </c>
+      <c r="T7" s="35" t="n">
+        <v>26586</v>
+      </c>
+      <c r="U7" s="35" t="n">
+        <v>23195</v>
+      </c>
+      <c r="V7" s="43" t="n">
+        <v>-3483</v>
+      </c>
+      <c r="W7" s="44" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="X7" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="31" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z7" s="32" t="inlineStr">
+        <is>
+          <t>10:10 breakdown: 5m low 22,950.90 breached OR-30L 22,981.35 | 10:15 retest: 5m high 22,974.15 tested OR-30L 22,981.35 as resistance | 10:20 confirmation: 5m close 22,936.05 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA7" s="32" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>PDL Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>TARGET HIT (3R)</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>22818.45</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>22850.55</v>
+      </c>
+      <c r="I8" s="26" t="n">
+        <v>22722.15</v>
+      </c>
+      <c r="J8" s="26" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="K8" s="26" t="n">
+        <v>22722.15</v>
+      </c>
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="M8" s="25" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="N8" s="26" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="O8" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P8" s="25" t="inlineStr">
+        <is>
+          <t>NIFTY 22700 PE</t>
+        </is>
+      </c>
+      <c r="Q8" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>121.21</v>
+      </c>
+      <c r="S8" s="26" t="n">
+        <v>162.55</v>
+      </c>
+      <c r="T8" s="28" t="n">
+        <v>23636</v>
+      </c>
+      <c r="U8" s="28" t="n">
+        <v>31697</v>
+      </c>
+      <c r="V8" s="29" t="n">
+        <v>7959</v>
+      </c>
+      <c r="W8" s="30" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="X8" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="24" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z8" s="25" t="inlineStr">
+        <is>
+          <t>11:40 breakdown: 5m low 22,839.70 breached PDL 22,845.25 | 11:45 retest: 5m high 22,841.90 tested PDL 22,845.25 as resistance | 11:55 confirmation: 5m close 22,818.45 held below PDL and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+        </is>
+      </c>
+      <c r="AA8" s="25" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (OR-30)</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>OR-30H Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
           <t>LONG</t>
         </is>
       </c>
-      <c r="F7" s="31" t="inlineStr">
-        <is>
-          <t>TRAILED (+1.87R)</t>
-        </is>
-      </c>
-      <c r="G7" s="33" t="n">
-        <v>22975.1</v>
-      </c>
-      <c r="H7" s="33" t="n">
-        <v>22941.5</v>
-      </c>
-      <c r="I7" s="33" t="n">
-        <v>23075.9</v>
-      </c>
-      <c r="J7" s="33" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="K7" s="33" t="n">
-        <v>23033.5</v>
-      </c>
-      <c r="L7" s="31" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="M7" s="32" t="inlineStr">
-        <is>
-          <t>Partial + Structure Trail</t>
-        </is>
-      </c>
-      <c r="N7" s="33" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="O7" s="34" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="P7" s="32" t="inlineStr">
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>TRAILED (+0.89R)</t>
+        </is>
+      </c>
+      <c r="G9" s="33" t="n">
+        <v>22712.95</v>
+      </c>
+      <c r="H9" s="33" t="n">
+        <v>22671.3</v>
+      </c>
+      <c r="I9" s="33" t="n">
+        <v>22900.38</v>
+      </c>
+      <c r="J9" s="33" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="K9" s="33" t="n">
+        <v>22749.9</v>
+      </c>
+      <c r="L9" s="31" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="M9" s="32" t="inlineStr">
+        <is>
+          <t>Structure Trail</t>
+        </is>
+      </c>
+      <c r="N9" s="33" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="O9" s="34" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P9" s="32" t="inlineStr">
+        <is>
+          <t>NIFTY 22800 CE</t>
+        </is>
+      </c>
+      <c r="Q9" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="R9" s="33" t="n">
+        <v>129.77</v>
+      </c>
+      <c r="S9" s="33" t="n">
+        <v>145.68</v>
+      </c>
+      <c r="T9" s="35" t="n">
+        <v>25305</v>
+      </c>
+      <c r="U9" s="35" t="n">
+        <v>28408</v>
+      </c>
+      <c r="V9" s="36" t="n">
+        <v>3004</v>
+      </c>
+      <c r="W9" s="37" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="X9" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="31" t="n">
+        <v>195</v>
+      </c>
+      <c r="Z9" s="32" t="inlineStr">
+        <is>
+          <t>10:25 breakout: 5m high 22,742.50 cleared OR-30H 22,690.45 | 10:50 retest: 5m low 22,676.30 tested OR-30H 22,690.45 as support | 10:55 confirmation: 5m close 22,712.95 held above OR-30H and VWAP</t>
+        </is>
+      </c>
+      <c r="AA9" s="32" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (OR-30)</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>OR-30 Breakout [1M Micro-Execution]</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>TARGET HIT (+3.59R)</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>22739.75</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <v>22696.5</v>
+      </c>
+      <c r="I10" s="26" t="n">
+        <v>22869.5</v>
+      </c>
+      <c r="J10" s="26" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="K10" s="26" t="n">
+        <v>22869.5</v>
+      </c>
+      <c r="L10" s="24" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="M10" s="25" t="inlineStr">
+        <is>
+          <t>Target (+3.0R Full Target Achieved)</t>
+        </is>
+      </c>
+      <c r="N10" s="26" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="O10" s="27" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="P10" s="25" t="inlineStr">
+        <is>
+          <t>NIFTY 22850 CE</t>
+        </is>
+      </c>
+      <c r="Q10" s="24" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>110.17</v>
+      </c>
+      <c r="S10" s="26" t="n">
+        <v>169.06</v>
+      </c>
+      <c r="T10" s="28" t="n">
+        <v>28644</v>
+      </c>
+      <c r="U10" s="28" t="n">
+        <v>43955</v>
+      </c>
+      <c r="V10" s="29" t="n">
+        <v>15311</v>
+      </c>
+      <c r="W10" s="30" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="X10" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="24" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z10" s="25" t="inlineStr">
+        <is>
+          <t>09:34 1M candle closed at 22,739.75 clearing OR-30 high with volume expansion above VWAP. Exited on full target expansion to 22,869.50 (+58.89 pts / +3.59R).</t>
+        </is>
+      </c>
+      <c r="AA10" s="25" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>PDH Support Flip [15M Macro Structure]</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>TARGET HIT (+3.47R)</t>
+        </is>
+      </c>
+      <c r="G11" s="33" t="n">
+        <v>22827.05</v>
+      </c>
+      <c r="H11" s="33" t="n">
+        <v>22782.3</v>
+      </c>
+      <c r="I11" s="33" t="n">
+        <v>22961.3</v>
+      </c>
+      <c r="J11" s="33" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="K11" s="33" t="n">
+        <v>22958.2</v>
+      </c>
+      <c r="L11" s="31" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="M11" s="32" t="inlineStr">
+        <is>
+          <t>Target 3 Hit (+3.0R Full Target / 15:14 IST Spot 22,958+)</t>
+        </is>
+      </c>
+      <c r="N11" s="33" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="O11" s="34" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="P11" s="32" t="inlineStr">
+        <is>
+          <t>NIFTY 22950 CE</t>
+        </is>
+      </c>
+      <c r="Q11" s="31" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R11" s="33" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="S11" s="33" t="n">
+        <v>158.61</v>
+      </c>
+      <c r="T11" s="35" t="n">
+        <v>25761</v>
+      </c>
+      <c r="U11" s="35" t="n">
+        <v>41239</v>
+      </c>
+      <c r="V11" s="36" t="n">
+        <v>15478</v>
+      </c>
+      <c r="W11" s="37" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="X11" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y11" s="31" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z11" s="32" t="inlineStr">
+        <is>
+          <t>11:15 IST 15M breakout and retest of PDH held above VWAP. Reached full target at 15:14 IST (+59.53 pts / +3.47R). Realized +Rs 15,478.00.</t>
+        </is>
+      </c>
+      <c r="AA11" s="32" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>PDH Support Flip [5M Micro-Execution]</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>TARGET HIT (+3.14R)</t>
+        </is>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>22980.7</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>22950.1</v>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>23072.5</v>
+      </c>
+      <c r="J12" s="26" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="K12" s="26" t="n">
+        <v>23053.45</v>
+      </c>
+      <c r="L12" s="24" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="M12" s="25" t="inlineStr">
+        <is>
+          <t>+3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="N12" s="26" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="O12" s="27" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P12" s="25" t="inlineStr">
         <is>
           <t>NIFTY 23100 CE</t>
         </is>
       </c>
-      <c r="Q7" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="R7" s="33" t="n">
-        <v>89.03</v>
-      </c>
-      <c r="S7" s="33" t="n">
-        <v>111.19</v>
-      </c>
-      <c r="T7" s="35" t="n">
-        <v>11574</v>
-      </c>
-      <c r="U7" s="35" t="n">
-        <v>14455</v>
-      </c>
-      <c r="V7" s="36" t="n">
-        <v>2808</v>
-      </c>
-      <c r="W7" s="37" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X7" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y7" s="31" t="n">
-        <v>130</v>
-      </c>
-      <c r="Z7" s="32" t="inlineStr">
-        <is>
-          <t>12:35 trendline breakout: 5m close 22,975.10 above descending line 22,967.34 (slope -1.59) | Anchored by swing highs at 11:55 (22,978.45) and 12:15 (22,972.10) | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+      <c r="Q12" s="24" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>78.67</v>
+      </c>
+      <c r="S12" s="26" t="n">
+        <v>114.32</v>
+      </c>
+      <c r="T12" s="28" t="n">
+        <v>20454</v>
+      </c>
+      <c r="U12" s="28" t="n">
+        <v>29723</v>
+      </c>
+      <c r="V12" s="29" t="n">
+        <v>9269</v>
+      </c>
+      <c r="W12" s="30" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="X12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="24" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z12" s="25" t="inlineStr">
+        <is>
+          <t>Paper trading forward test executed on 5M timeframe. +3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="AA12" s="25" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (OR-30)</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>OR-30H Support Flip [5M Micro-Execution]</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>TARGET HIT (+3.34R)</t>
+        </is>
+      </c>
+      <c r="G13" s="33" t="n">
+        <v>23006.25</v>
+      </c>
+      <c r="H13" s="33" t="n">
+        <v>22974.75</v>
+      </c>
+      <c r="I13" s="33" t="n">
+        <v>23100.75</v>
+      </c>
+      <c r="J13" s="33" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K13" s="33" t="n">
+        <v>23053.1</v>
+      </c>
+      <c r="L13" s="31" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="M13" s="32" t="inlineStr">
+        <is>
+          <t>+3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="N13" s="33" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="O13" s="34" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P13" s="32" t="inlineStr">
+        <is>
+          <t>NIFTY 23100 CE</t>
+        </is>
+      </c>
+      <c r="Q13" s="31" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R13" s="33" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="S13" s="33" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="T13" s="35" t="n">
+        <v>16190</v>
+      </c>
+      <c r="U13" s="35" t="n">
+        <v>25610</v>
+      </c>
+      <c r="V13" s="36" t="n">
+        <v>9420</v>
+      </c>
+      <c r="W13" s="37" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="X13" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y13" s="31" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z13" s="32" t="inlineStr">
+        <is>
+          <t>Paper trading forward test executed on 5M timeframe. +3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="AA13" s="32" t="inlineStr">
+        <is>
+          <t>paper</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z7"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>No trades recorded for this strategy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:AA13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
